--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -553,7 +553,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 22/09/2026 12:12 | Nguồn: classroom.khanacademy.org</t>
+          <t>Thời gian thống kê: 22/09/2026 13:00 | Nguồn: classroom.khanacademy.org</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -553,7 +553,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 22/09/2026 13:00 | Nguồn: classroom.khanacademy.org</t>
+          <t>Thời gian thống kê: 22/09/2026 13:16 | Nguồn: classroom.khanacademy.org</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -553,7 +553,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 22/09/2026 13:16 | Nguồn: classroom.khanacademy.org</t>
+          <t>Thời gian thống kê: 22/09/2026 13:17 | Nguồn: classroom.khanacademy.org</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -553,7 +553,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 22/09/2026 13:17 | Nguồn: classroom.khanacademy.org</t>
+          <t>Thời gian thống kê: 22/09/2026 13:26 | Nguồn: classroom.khanacademy.org</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -553,7 +553,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 22/09/2026 13:26 | Nguồn: classroom.khanacademy.org</t>
+          <t>Thời gian thống kê: 22/09/2026 13:27 | Nguồn: classroom.khanacademy.org</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -553,7 +553,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 22/09/2026 13:27 | Nguồn: classroom.khanacademy.org</t>
+          <t>Thời gian thống kê: 22/09/2026 22:32 | Nguồn: classroom.khanacademy.org</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
         <v>47</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G6" s="11" t="n">
         <v>0.1</v>
@@ -795,7 +795,7 @@
         <v>10</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -1188,7 +1188,7 @@
         <v>821</v>
       </c>
       <c r="F25" s="14" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G25" s="15" t="n">
         <v>0.9</v>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -553,7 +553,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 22/09/2026 22:32 | Nguồn: classroom.khanacademy.org</t>
+          <t>Thời gian thống kê: 24/09/2026 18:00 | Nguồn: classroom.khanacademy.org</t>
         </is>
       </c>
     </row>
@@ -618,10 +618,10 @@
         <v>44</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>6.6</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -647,10 +647,10 @@
         <v>47</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -676,10 +676,10 @@
         <v>44</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -792,10 +792,10 @@
         <v>44</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -850,10 +850,10 @@
         <v>41</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>3.2</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -908,10 +908,10 @@
         <v>46</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>5.2</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -1024,7 +1024,7 @@
         <v>43</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G19" s="7" t="n">
         <v>0.3</v>
@@ -1188,10 +1188,10 @@
         <v>821</v>
       </c>
       <c r="F25" s="14" t="n">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
     </row>
   </sheetData>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -553,7 +553,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 24/09/2026 18:00 | Nguồn: classroom.khanacademy.org</t>
+          <t>Thời gian thống kê: 26/09/2026 15:20 | Nguồn: classroom.khanacademy.org</t>
         </is>
       </c>
     </row>
@@ -650,7 +650,7 @@
         <v>9</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -676,7 +676,7 @@
         <v>44</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>0.2</v>
@@ -792,10 +792,10 @@
         <v>44</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -850,10 +850,10 @@
         <v>41</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -908,10 +908,10 @@
         <v>46</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -1082,7 +1082,7 @@
         <v>37</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G21" s="7" t="n">
         <v>0.1</v>
@@ -1111,7 +1111,7 @@
         <v>50</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G22" s="11" t="n">
         <v>0</v>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -553,7 +553,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 26/09/2026 15:20 | Nguồn: classroom.khanacademy.org</t>
+          <t>Thời gian thống kê: 26/09/2026 22:25 | Nguồn: classroom.khanacademy.org</t>
         </is>
       </c>
     </row>
@@ -792,10 +792,10 @@
         <v>44</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -1188,7 +1188,7 @@
         <v>821</v>
       </c>
       <c r="F25" s="14" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G25" s="15" t="n">
         <v>0.7</v>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -553,7 +553,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 26/09/2026 22:25 | Nguồn: classroom.khanacademy.org</t>
+          <t>Thời gian thống kê: 27/09/2026 11:00 | Nguồn: classroom.khanacademy.org</t>
         </is>
       </c>
     </row>
@@ -618,10 +618,10 @@
         <v>44</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>6.3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -647,10 +647,10 @@
         <v>47</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -850,10 +850,10 @@
         <v>41</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -908,10 +908,10 @@
         <v>46</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -1111,10 +1111,10 @@
         <v>50</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -1188,10 +1188,10 @@
         <v>821</v>
       </c>
       <c r="F25" s="14" t="n">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
     </row>
   </sheetData>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -553,7 +553,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 27/09/2026 11:00 | Nguồn: classroom.khanacademy.org</t>
+          <t>Thời gian thống kê: 27/09/2026 11:02 | Nguồn: classroom.khanacademy.org</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -531,7 +531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -553,7 +553,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 27/09/2026 11:02 | Nguồn: classroom.khanacademy.org</t>
+          <t>Thời gian thống kê: 29/09/2026 11:00 | Nguồn: classroom.khanacademy.org</t>
         </is>
       </c>
     </row>
@@ -618,10 +618,10 @@
         <v>44</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>5</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -647,10 +647,10 @@
         <v>47</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -659,12 +659,12 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>FHGUSN4Z</t>
+          <t>UWTVBASW</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>10A4_Năm học 2026-2027_Văn Thị Bích Thùy</t>
+          <t>10A3_Năm học 2026-2027_Văn Thị Bích Thùy</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -673,10 +673,10 @@
         </is>
       </c>
       <c r="E7" s="6" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>0.2</v>
@@ -688,12 +688,12 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>4NH4T2A4</t>
+          <t>FHGUSN4Z</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>10A5_Năm học 2026-2027_Nguyễn Ngọc Thịnh</t>
+          <t>10A4_Năm học 2026-2027_Văn Thị Bích Thùy</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
@@ -702,13 +702,13 @@
         </is>
       </c>
       <c r="E8" s="10" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -717,12 +717,12 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>VZQP4YAF</t>
+          <t>4NH4T2A4</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>10A6_Năm học 2026-2027_Nguyễn Ngọc Thịnh</t>
+          <t>10A5_Năm học 2026-2027_Nguyễn Ngọc Thịnh</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -731,13 +731,13 @@
         </is>
       </c>
       <c r="E9" s="6" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -746,12 +746,12 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>KMR6W4FR</t>
+          <t>VZQP4YAF</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>10A7_Năm học 2026-2027_Nguyễn Chí Huy</t>
+          <t>10A6_Năm học 2026-2027_Nguyễn Ngọc Thịnh</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
@@ -760,13 +760,13 @@
         </is>
       </c>
       <c r="E10" s="10" t="n">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -775,12 +775,12 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>DZWFS5NS</t>
+          <t>KMR6W4FR</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>10A8_Năm học 2026-2027_Nguyễn Thành Thái</t>
+          <t>10A7_Năm học 2026-2027_Nguyễn Chí Huy</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -789,13 +789,13 @@
         </is>
       </c>
       <c r="E11" s="6" t="n">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -804,27 +804,27 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>PJP8ZHQ5</t>
+          <t>DZWFS5NS</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>11A1_Năm học 2026-2027_Nguyễn Ngọc Thịnh</t>
+          <t>10A8_Năm học 2026-2027_Nguyễn Thành Thái</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Toán 11</t>
+          <t>Toán 10</t>
         </is>
       </c>
       <c r="E12" s="10" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -833,12 +833,12 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>UQ77Z4F8</t>
+          <t>PJP8ZHQ5</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>11A2_Năm học 2026-2027_Nguyễn Thị Yến Linh</t>
+          <t>11A1_Năm học 2026-2027_Nguyễn Ngọc Thịnh</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -850,10 +850,10 @@
         <v>41</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -862,12 +862,12 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>6JZUDEYH</t>
+          <t>UQ77Z4F8</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>11A3_Năm Học 2026-2027_Mai Thành Công</t>
+          <t>11A2_Năm học 2026-2027_Nguyễn Thị Yến Linh</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
@@ -876,10 +876,10 @@
         </is>
       </c>
       <c r="E14" s="10" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G14" s="11" t="n">
         <v>0</v>
@@ -891,12 +891,12 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>NFPJ3YUZ</t>
+          <t>6JZUDEYH</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>11A4_Năm học 2026-2027_Nguyễn Thị Yến Linh</t>
+          <t>11A3_Năm Học 2026-2027_Mai Thành Công</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -905,13 +905,13 @@
         </is>
       </c>
       <c r="E15" s="6" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -920,12 +920,12 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>EJ5JBTPM</t>
+          <t>NFPJ3YUZ</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>11A5_ Năm Học 2026-2027_Nguyễn Ngọc Thịnh</t>
+          <t>11A4_Năm học 2026-2027_Nguyễn Thị Yến Linh</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="E16" s="10" t="n">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" s="11" t="n">
         <v>0</v>
@@ -949,12 +949,12 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>N6D6F43M</t>
+          <t>EJ5JBTPM</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>11A6_Năm học 2026-2027_Mai Thành Công</t>
+          <t>11A5_ Năm Học 2026-2027_Nguyễn Ngọc Thịnh</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="E17" s="6" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>0</v>
@@ -978,21 +978,21 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>Y4KXVHFH</t>
+          <t>N6D6F43M</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>12A1-Năm học 2026-2027_Trần Thị Bội Nhung</t>
+          <t>11A6_Năm học 2026-2027_Mai Thành Công</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>Toán 12</t>
+          <t>Toán 11</t>
         </is>
       </c>
       <c r="E18" s="10" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F18" s="10" t="n">
         <v>0</v>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>7B39B8FY</t>
+          <t>Y4KXVHFH</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>12A2 - Năm học 2026-2027_Nguyễn Thành Thái</t>
+          <t>12A1-Năm học 2026-2027_Trần Thị Bội Nhung</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="E19" s="6" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>2DXNAW8H</t>
+          <t>7B39B8FY</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>12A3-Năm học 2026-2027_Mai Thành Công</t>
+          <t>12A2 - Năm học 2026-2027_Nguyễn Thành Thái</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
@@ -1050,13 +1050,13 @@
         </is>
       </c>
       <c r="E20" s="10" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -1065,12 +1065,12 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>2T2BZU9H</t>
+          <t>2DXNAW8H</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>12A4-Năm học 2026-2027_Nguyễn Thành Thái</t>
+          <t>12A3-Năm học 2026-2027_Mai Thành Công</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -1079,13 +1079,13 @@
         </is>
       </c>
       <c r="E21" s="6" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>MF9R2SND</t>
+          <t>2T2BZU9H</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>12A5 - Năm học 2026-2027_Trần Thị Bội Nhung</t>
+          <t>12A4-Năm học 2026-2027_Nguyễn Thành Thái</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="E22" s="10" t="n">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>BQKUESU3</t>
+          <t>MF9R2SND</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>12A6 _Năm học 2026-2027_Nguyễn Thành Thái</t>
+          <t>12A5 - Năm học 2026-2027_Trần Thị Bội Nhung</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -1137,13 +1137,13 @@
         </is>
       </c>
       <c r="E23" s="6" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -1152,53 +1152,82 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
+          <t>BQKUESU3</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>12A6 _Năm học 2026-2027_Nguyễn Thành Thái</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>Toán 12</t>
+        </is>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="F24" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" s="11" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
           <t>Q96EYDVA</t>
         </is>
       </c>
-      <c r="C24" s="9" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>12A7 - Năm học 2026 - 2027_Trần Thị Bội Nhung</t>
         </is>
       </c>
-      <c r="D24" s="8" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>Toán 12</t>
         </is>
       </c>
-      <c r="E24" s="10" t="n">
+      <c r="E25" s="6" t="n">
         <v>28</v>
       </c>
-      <c r="F24" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" ht="26" customHeight="1">
-      <c r="A25" s="12" t="inlineStr">
+      <c r="F25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" ht="26" customHeight="1">
+      <c r="A26" s="12" t="inlineStr">
         <is>
           <t>TỔNG CỘNG / TRUNG BÌNH TOÀN BỘ:</t>
         </is>
       </c>
-      <c r="B25" s="13" t="n"/>
-      <c r="C25" s="13" t="n"/>
-      <c r="D25" s="13" t="n"/>
-      <c r="E25" s="14" t="n">
-        <v>821</v>
-      </c>
-      <c r="F25" s="14" t="n">
-        <v>152</v>
-      </c>
-      <c r="G25" s="15" t="n">
-        <v>0.6</v>
+      <c r="B26" s="13" t="n"/>
+      <c r="C26" s="13" t="n"/>
+      <c r="D26" s="13" t="n"/>
+      <c r="E26" s="14" t="n">
+        <v>866</v>
+      </c>
+      <c r="F26" s="14" t="n">
+        <v>121</v>
+      </c>
+      <c r="G26" s="15" t="n">
+        <v>0.4</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A26:D26"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A25:D25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -553,7 +553,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 29/09/2026 11:00 | Nguồn: classroom.khanacademy.org</t>
+          <t>Thời gian thống kê: 30/09/2026 20:09 | Nguồn: classroom.khanacademy.org</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
         <v>20</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -676,10 +676,10 @@
         <v>45</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -705,10 +705,10 @@
         <v>44</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -734,7 +734,7 @@
         <v>47</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G9" s="7" t="n">
         <v>1.5</v>
@@ -818,13 +818,13 @@
         </is>
       </c>
       <c r="E12" s="10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>2.2</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -879,7 +879,7 @@
         <v>41</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G14" s="11" t="n">
         <v>0</v>
@@ -1053,7 +1053,7 @@
         <v>43</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G20" s="11" t="n">
         <v>0.1</v>
@@ -1140,10 +1140,10 @@
         <v>50</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -1214,13 +1214,13 @@
       <c r="C26" s="13" t="n"/>
       <c r="D26" s="13" t="n"/>
       <c r="E26" s="14" t="n">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>121</v>
+        <v>147</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
     </row>
   </sheetData>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -553,7 +553,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 30/09/2026 20:09 | Nguồn: classroom.khanacademy.org</t>
+          <t>Thời gian thống kê: 01/10/2026 15:27 | Nguồn: classroom.khanacademy.org</t>
         </is>
       </c>
     </row>
@@ -618,10 +618,10 @@
         <v>44</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -647,10 +647,10 @@
         <v>47</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -705,7 +705,7 @@
         <v>44</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G8" s="11" t="n">
         <v>0.5</v>
@@ -824,7 +824,7 @@
         <v>35</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -1217,10 +1217,10 @@
         <v>867</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>147</v>
+        <v>131</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -553,7 +553,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 01/10/2026 15:27 | Nguồn: classroom.khanacademy.org</t>
+          <t>Thời gian thống kê: 02/10/2026 11:00 | Nguồn: classroom.khanacademy.org</t>
         </is>
       </c>
     </row>
@@ -618,10 +618,10 @@
         <v>44</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -676,10 +676,10 @@
         <v>45</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>0.8</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -705,10 +705,10 @@
         <v>44</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>0.5</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -763,10 +763,10 @@
         <v>45</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -821,10 +821,10 @@
         <v>45</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -1053,7 +1053,7 @@
         <v>43</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G20" s="11" t="n">
         <v>0.1</v>
@@ -1140,10 +1140,10 @@
         <v>50</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -1217,10 +1217,10 @@
         <v>867</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>131</v>
+        <v>190</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
     </row>
   </sheetData>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -553,7 +553,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 02/10/2026 11:00 | Nguồn: classroom.khanacademy.org</t>
+          <t>Thời gian thống kê: 03/10/2026 13:51 | Nguồn: classroom.khanacademy.org</t>
         </is>
       </c>
     </row>
@@ -618,10 +618,10 @@
         <v>44</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -647,10 +647,10 @@
         <v>47</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -676,10 +676,10 @@
         <v>45</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -705,10 +705,10 @@
         <v>44</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -734,10 +734,10 @@
         <v>47</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -763,10 +763,10 @@
         <v>45</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -821,7 +821,7 @@
         <v>45</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G12" s="11" t="n">
         <v>2.9</v>
@@ -876,13 +876,13 @@
         </is>
       </c>
       <c r="E14" s="10" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -908,7 +908,7 @@
         <v>44</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" s="7" t="n">
         <v>0</v>
@@ -937,10 +937,10 @@
         <v>46</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -995,7 +995,7 @@
         <v>37</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" s="11" t="n">
         <v>0</v>
@@ -1024,7 +1024,7 @@
         <v>35</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" s="7" t="n">
         <v>0</v>
@@ -1053,7 +1053,7 @@
         <v>43</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G20" s="11" t="n">
         <v>0.1</v>
@@ -1082,7 +1082,7 @@
         <v>40</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G21" s="7" t="n">
         <v>0</v>
@@ -1111,10 +1111,10 @@
         <v>37</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -1140,10 +1140,10 @@
         <v>50</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -1198,7 +1198,7 @@
         <v>28</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25" s="7" t="n">
         <v>0</v>
@@ -1214,13 +1214,13 @@
       <c r="C26" s="13" t="n"/>
       <c r="D26" s="13" t="n"/>
       <c r="E26" s="14" t="n">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>190</v>
+        <v>233</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
     </row>
   </sheetData>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -553,7 +553,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 03/10/2026 13:51 | Nguồn: classroom.khanacademy.org</t>
+          <t>Thời gian thống kê: 03/10/2026 23:30 | Nguồn: classroom.khanacademy.org</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
         <v>14</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -676,10 +676,10 @@
         <v>45</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -705,10 +705,10 @@
         <v>44</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -763,10 +763,10 @@
         <v>45</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -821,7 +821,7 @@
         <v>45</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G12" s="11" t="n">
         <v>2.9</v>
@@ -879,10 +879,10 @@
         <v>40</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -1024,10 +1024,10 @@
         <v>35</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -1082,10 +1082,10 @@
         <v>40</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
@@ -1140,10 +1140,10 @@
         <v>50</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -1169,7 +1169,7 @@
         <v>42</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G24" s="11" t="n">
         <v>0.1</v>
@@ -1198,10 +1198,10 @@
         <v>28</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="26" ht="26" customHeight="1">
@@ -1217,10 +1217,10 @@
         <v>866</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>233</v>
+        <v>278</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
     </row>
   </sheetData>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -553,7 +553,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 03/10/2026 23:30 | Nguồn: classroom.khanacademy.org</t>
+          <t>Thời gian thống kê: 04/10/2026 10:38 | Nguồn: classroom.khanacademy.org</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
         <v>44</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G5" s="7" t="n">
         <v>1</v>
@@ -647,7 +647,7 @@
         <v>47</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G6" s="11" t="n">
         <v>0.4</v>
@@ -824,7 +824,7 @@
         <v>34</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -882,7 +882,7 @@
         <v>12</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -937,10 +937,10 @@
         <v>46</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -966,7 +966,7 @@
         <v>33</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" s="7" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>40</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
@@ -1198,10 +1198,10 @@
         <v>28</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="26" ht="26" customHeight="1">
@@ -1217,7 +1217,7 @@
         <v>866</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="G26" s="15" t="n">
         <v>1.1</v>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -553,7 +553,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 04/10/2026 10:38 | Nguồn: classroom.khanacademy.org</t>
+          <t>Thời gian thống kê: 04/10/2026 11:00 | Nguồn: classroom.khanacademy.org</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
         <v>13</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -1082,10 +1082,10 @@
         <v>40</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
@@ -1217,7 +1217,7 @@
         <v>866</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="G26" s="15" t="n">
         <v>1.1</v>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -553,7 +553,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 04/10/2026 11:00 | Nguồn: classroom.khanacademy.org</t>
+          <t>Thời gian thống kê: 04/10/2026 21:31 | Nguồn: classroom.khanacademy.org</t>
         </is>
       </c>
     </row>
@@ -618,10 +618,10 @@
         <v>44</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -679,7 +679,7 @@
         <v>44</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -705,10 +705,10 @@
         <v>44</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -763,10 +763,10 @@
         <v>45</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -824,7 +824,7 @@
         <v>34</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -879,10 +879,10 @@
         <v>40</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -937,10 +937,10 @@
         <v>46</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -966,7 +966,7 @@
         <v>33</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G17" s="7" t="n">
         <v>0</v>
@@ -1027,7 +1027,7 @@
         <v>9</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -1056,7 +1056,7 @@
         <v>10</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -1082,7 +1082,7 @@
         <v>40</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G21" s="7" t="n">
         <v>0.8</v>
@@ -1140,10 +1140,10 @@
         <v>50</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -1198,10 +1198,10 @@
         <v>28</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="26" ht="26" customHeight="1">
@@ -1217,10 +1217,10 @@
         <v>866</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>292</v>
+        <v>328</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -553,7 +553,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 04/10/2026 21:31 | Nguồn: classroom.khanacademy.org</t>
+          <t>Thời gian thống kê: 05/10/2026 11:00 | Nguồn: classroom.khanacademy.org</t>
         </is>
       </c>
     </row>
@@ -618,10 +618,10 @@
         <v>44</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -647,10 +647,10 @@
         <v>47</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -734,10 +734,10 @@
         <v>47</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -824,7 +824,7 @@
         <v>34</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -879,10 +879,10 @@
         <v>40</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -937,10 +937,10 @@
         <v>46</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -1027,7 +1027,7 @@
         <v>9</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -1053,7 +1053,7 @@
         <v>43</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G20" s="11" t="n">
         <v>0.2</v>
@@ -1085,7 +1085,7 @@
         <v>22</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
@@ -1111,10 +1111,10 @@
         <v>37</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -1140,10 +1140,10 @@
         <v>50</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -1198,10 +1198,10 @@
         <v>28</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="26" ht="26" customHeight="1">
@@ -1220,7 +1220,7 @@
         <v>328</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -553,7 +553,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 05/10/2026 11:00 | Nguồn: classroom.khanacademy.org</t>
+          <t>Thời gian thống kê: 06/10/2026 11:00 | Nguồn: classroom.khanacademy.org</t>
         </is>
       </c>
     </row>
@@ -618,10 +618,10 @@
         <v>44</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>3.2</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -676,10 +676,10 @@
         <v>45</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -708,7 +708,7 @@
         <v>40</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -734,10 +734,10 @@
         <v>47</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -763,10 +763,10 @@
         <v>45</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -879,10 +879,10 @@
         <v>40</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>2.6</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -908,10 +908,10 @@
         <v>44</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -937,10 +937,10 @@
         <v>46</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>3.3</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -995,10 +995,10 @@
         <v>37</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -1027,7 +1027,7 @@
         <v>9</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -1053,10 +1053,10 @@
         <v>43</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -1085,7 +1085,7 @@
         <v>22</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
@@ -1140,10 +1140,10 @@
         <v>50</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -1169,10 +1169,10 @@
         <v>42</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
@@ -1198,10 +1198,10 @@
         <v>28</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="26" ht="26" customHeight="1">
@@ -1217,10 +1217,10 @@
         <v>866</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
     </row>
   </sheetData>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -553,7 +553,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 06/10/2026 11:00 | Nguồn: classroom.khanacademy.org</t>
+          <t>Thời gian thống kê: 06/10/2026 13:08 | Nguồn: classroom.khanacademy.org</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
         <v>45</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G10" s="11" t="n">
         <v>2.6</v>
@@ -937,10 +937,10 @@
         <v>46</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -995,7 +995,7 @@
         <v>37</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G18" s="11" t="n">
         <v>0.2</v>
@@ -1082,7 +1082,7 @@
         <v>40</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G21" s="7" t="n">
         <v>0.2</v>
@@ -1217,7 +1217,7 @@
         <v>866</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="G26" s="15" t="n">
         <v>1.9</v>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -553,7 +553,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 06/10/2026 13:08 | Nguồn: classroom.khanacademy.org</t>
+          <t>Thời gian thống kê: 06/10/2026 20:06 | Nguồn: classroom.khanacademy.org</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
         <v>39</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -734,7 +734,7 @@
         <v>47</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G9" s="7" t="n">
         <v>0.4</v>
@@ -908,7 +908,7 @@
         <v>44</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G15" s="7" t="n">
         <v>0.2</v>
@@ -937,10 +937,10 @@
         <v>46</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -995,10 +995,10 @@
         <v>37</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -1024,10 +1024,10 @@
         <v>35</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -1082,10 +1082,10 @@
         <v>40</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
@@ -1217,7 +1217,7 @@
         <v>866</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>368</v>
+        <v>384</v>
       </c>
       <c r="G26" s="15" t="n">
         <v>1.9</v>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -16,8 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="4">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,8 +45,17 @@
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -57,8 +68,20 @@
         <bgColor rgb="001B365D"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4F8FC"/>
+        <bgColor rgb="00F4F8FC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EBF2FA"/>
+        <bgColor rgb="00EBF2FA"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -80,11 +103,25 @@
         <color rgb="00D3D3D3"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D3D3D3"/>
+      </right>
+      <top style="thin">
+        <color rgb="001B365D"/>
+      </top>
+      <bottom style="double">
+        <color rgb="001B365D"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -94,6 +131,40 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -460,7 +531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -482,7 +553,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 07/10/2026 11:00 | Nguồn: classroom.khanacademy.org</t>
+          <t>Thời gian thống kê: 07/10/2026 17:29 | Nguồn: classroom.khanacademy.org</t>
         </is>
       </c>
     </row>
@@ -524,8 +595,637 @@
         </is>
       </c>
     </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>GC65CJ23</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>10A1_Năm học 2026-2027_Nguyễn Thị Yến Linh</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Toán 10</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>44</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="G5" s="7" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>H4S4C7P2</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>10A2_Năm học 2026-2027_Trần Minh Mẫn</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Toán 10</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>47</v>
+      </c>
+      <c r="F6" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="G6" s="11" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>UWTVBASW</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>10A3_Năm học 2026-2027_Văn Thị Bích Thùy</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Toán 10</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="G7" s="7" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>FHGUSN4Z</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>10A4_Năm học 2026-2027_Văn Thị Bích Thùy</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Toán 10</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="F8" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="G8" s="11" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>4NH4T2A4</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>10A5_Năm học 2026-2027_Nguyễn Ngọc Thịnh</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Toán 10</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>47</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G9" s="7" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>VZQP4YAF</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>10A6_Năm học 2026-2027_Nguyễn Ngọc Thịnh</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Toán 10</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="F10" s="10" t="n">
+        <v>24</v>
+      </c>
+      <c r="G10" s="11" t="n">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>KMR6W4FR</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>10A7_Năm học 2026-2027_Nguyễn Chí Huy</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Toán 10</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>DZWFS5NS</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>10A8_Năm học 2026-2027_Nguyễn Thành Thái</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>Toán 10</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="F12" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="G12" s="11" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>PJP8ZHQ5</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>11A1_Năm học 2026-2027_Nguyễn Ngọc Thịnh</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Toán 11</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>UQ77Z4F8</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>11A2_Năm học 2026-2027_Nguyễn Thị Yến Linh</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>Toán 11</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="F14" s="10" t="n">
+        <v>38</v>
+      </c>
+      <c r="G14" s="11" t="n">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>6JZUDEYH</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>11A3_Năm Học 2026-2027_Mai Thành Công</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Toán 11</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>44</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G15" s="7" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>NFPJ3YUZ</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>11A4_Năm học 2026-2027_Nguyễn Thị Yến Linh</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>Toán 11</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>46</v>
+      </c>
+      <c r="F16" s="10" t="n">
+        <v>32</v>
+      </c>
+      <c r="G16" s="11" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>EJ5JBTPM</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>11A5_ Năm Học 2026-2027_Nguyễn Ngọc Thịnh</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Toán 11</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G17" s="7" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>N6D6F43M</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>11A6_Năm học 2026-2027_Mai Thành Công</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>Toán 11</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="F18" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="G18" s="11" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Y4KXVHFH</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>12A1-Năm học 2026-2027_Trần Thị Bội Nhung</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Toán 12</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="G19" s="7" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>7B39B8FY</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>12A2 - Năm học 2026-2027_Nguyễn Thành Thái</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>Toán 12</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="n">
+        <v>43</v>
+      </c>
+      <c r="F20" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="G20" s="11" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>2DXNAW8H</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>12A3-Năm học 2026-2027_Mai Thành Công</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Toán 12</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="G21" s="7" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>2T2BZU9H</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>12A4-Năm học 2026-2027_Nguyễn Thành Thái</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>Toán 12</t>
+        </is>
+      </c>
+      <c r="E22" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="F22" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="G22" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>MF9R2SND</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>12A5 - Năm học 2026-2027_Trần Thị Bội Nhung</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>Toán 12</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="G23" s="7" t="n">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>BQKUESU3</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>12A6 _Năm học 2026-2027_Nguyễn Thành Thái</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>Toán 12</t>
+        </is>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="F24" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Q96EYDVA</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>12A7 - Năm học 2026 - 2027_Trần Thị Bội Nhung</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>Toán 12</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="G25" s="7" t="n">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="26" ht="26" customHeight="1">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>TỔNG CỘNG / TRUNG BÌNH TOÀN BỘ:</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="n"/>
+      <c r="C26" s="13" t="n"/>
+      <c r="D26" s="13" t="n"/>
+      <c r="E26" s="14" t="n">
+        <v>866</v>
+      </c>
+      <c r="F26" s="14" t="n">
+        <v>374</v>
+      </c>
+      <c r="G26" s="15" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
+    <mergeCell ref="A26:D26"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -553,7 +553,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 07/10/2026 17:29 | Nguồn: classroom.khanacademy.org</t>
+          <t>Thời gian thống kê: 08/10/2026 11:18 | Nguồn: classroom.khanacademy.org</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
         <v>40</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -673,13 +673,13 @@
         </is>
       </c>
       <c r="E7" s="6" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -734,7 +734,7 @@
         <v>47</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G9" s="7" t="n">
         <v>0.4</v>
@@ -763,7 +763,7 @@
         <v>45</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G10" s="11" t="n">
         <v>2.6</v>
@@ -789,13 +789,13 @@
         </is>
       </c>
       <c r="E11" s="6" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -821,10 +821,10 @@
         <v>45</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -908,7 +908,7 @@
         <v>44</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G15" s="7" t="n">
         <v>0.2</v>
@@ -937,10 +937,10 @@
         <v>46</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>7</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -995,7 +995,7 @@
         <v>37</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G18" s="11" t="n">
         <v>1.1</v>
@@ -1053,7 +1053,7 @@
         <v>43</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G20" s="11" t="n">
         <v>0.1</v>
@@ -1085,7 +1085,7 @@
         <v>27</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
@@ -1140,10 +1140,10 @@
         <v>50</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -1214,10 +1214,10 @@
       <c r="C26" s="13" t="n"/>
       <c r="D26" s="13" t="n"/>
       <c r="E26" s="14" t="n">
-        <v>866</v>
+        <v>873</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="G26" s="15" t="n">
         <v>2</v>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -553,7 +553,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 08/10/2026 11:18 | Nguồn: classroom.khanacademy.org</t>
+          <t>Thời gian thống kê: 08/10/2026 14:34 | Nguồn: classroom.khanacademy.org</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
         <v>40</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -734,10 +734,10 @@
         <v>47</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -1027,7 +1027,7 @@
         <v>12</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -1217,7 +1217,7 @@
         <v>873</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G26" s="15" t="n">
         <v>2</v>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -553,7 +553,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 08/10/2026 14:34 | Nguồn: classroom.khanacademy.org</t>
+          <t>Thời gian thống kê: 09/10/2026 15:02 | Nguồn: classroom.khanacademy.org</t>
         </is>
       </c>
     </row>
@@ -618,10 +618,10 @@
         <v>44</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -647,7 +647,7 @@
         <v>47</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G6" s="11" t="n">
         <v>0.2</v>
@@ -676,10 +676,10 @@
         <v>46</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>3.3</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -705,10 +705,10 @@
         <v>44</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>4.5</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -731,13 +731,13 @@
         </is>
       </c>
       <c r="E9" s="6" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -760,13 +760,13 @@
         </is>
       </c>
       <c r="E10" s="10" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -789,13 +789,13 @@
         </is>
       </c>
       <c r="E11" s="6" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>0.3</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -821,7 +821,7 @@
         <v>45</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G12" s="11" t="n">
         <v>0.3</v>
@@ -937,10 +937,10 @@
         <v>46</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>7.9</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -995,10 +995,10 @@
         <v>37</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -1053,7 +1053,7 @@
         <v>43</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G20" s="11" t="n">
         <v>0.1</v>
@@ -1140,10 +1140,10 @@
         <v>50</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -1214,13 +1214,13 @@
       <c r="C26" s="13" t="n"/>
       <c r="D26" s="13" t="n"/>
       <c r="E26" s="14" t="n">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>365</v>
+        <v>337</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
     </row>
   </sheetData>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -553,7 +553,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 09/10/2026 15:02 | Nguồn: classroom.khanacademy.org</t>
+          <t>Thời gian thống kê: 09/10/2026 20:56 | Nguồn: classroom.khanacademy.org</t>
         </is>
       </c>
     </row>
@@ -650,7 +650,7 @@
         <v>4</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -734,10 +734,10 @@
         <v>46</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -763,10 +763,10 @@
         <v>46</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -908,10 +908,10 @@
         <v>44</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -937,10 +937,10 @@
         <v>46</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>8.4</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -998,7 +998,7 @@
         <v>16</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -1027,7 +1027,7 @@
         <v>12</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -1217,10 +1217,10 @@
         <v>874</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -553,7 +553,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 09/10/2026 20:56 | Nguồn: classroom.khanacademy.org</t>
+          <t>Thời gian thống kê: 10/10/2026 19:56 | Nguồn: classroom.khanacademy.org</t>
         </is>
       </c>
     </row>
@@ -676,10 +676,10 @@
         <v>46</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -705,10 +705,10 @@
         <v>44</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -734,10 +734,10 @@
         <v>46</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -763,10 +763,10 @@
         <v>46</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -792,10 +792,10 @@
         <v>40</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -821,10 +821,10 @@
         <v>45</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -908,10 +908,10 @@
         <v>44</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -937,10 +937,10 @@
         <v>46</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>9.1</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -995,10 +995,10 @@
         <v>37</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -1027,7 +1027,7 @@
         <v>12</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -1050,13 +1050,13 @@
         </is>
       </c>
       <c r="E20" s="10" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>0.1</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -1111,10 +1111,10 @@
         <v>37</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -1140,10 +1140,10 @@
         <v>50</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -1169,10 +1169,10 @@
         <v>42</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
@@ -1214,13 +1214,13 @@
       <c r="C26" s="13" t="n"/>
       <c r="D26" s="13" t="n"/>
       <c r="E26" s="14" t="n">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>344</v>
+        <v>400</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
     </row>
   </sheetData>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -553,7 +553,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 10/10/2026 19:56 | Nguồn: classroom.khanacademy.org</t>
+          <t>Thời gian thống kê: 12/10/2026 15:55 | Nguồn: classroom.khanacademy.org</t>
         </is>
       </c>
     </row>
@@ -618,10 +618,10 @@
         <v>44</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>7.6</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -647,10 +647,10 @@
         <v>47</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -676,10 +676,10 @@
         <v>46</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -705,10 +705,10 @@
         <v>44</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -731,13 +731,13 @@
         </is>
       </c>
       <c r="E9" s="6" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -760,13 +760,13 @@
         </is>
       </c>
       <c r="E10" s="10" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -792,10 +792,10 @@
         <v>40</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -821,10 +821,10 @@
         <v>45</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -847,10 +847,10 @@
         </is>
       </c>
       <c r="E13" s="6" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G13" s="7" t="n">
         <v>0</v>
@@ -879,10 +879,10 @@
         <v>40</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>7.2</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -908,10 +908,10 @@
         <v>44</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -937,7 +937,7 @@
         <v>46</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G16" s="11" t="n">
         <v>9.9</v>
@@ -966,10 +966,10 @@
         <v>33</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -998,7 +998,7 @@
         <v>20</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -1053,10 +1053,10 @@
         <v>44</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -1082,10 +1082,10 @@
         <v>40</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
@@ -1111,10 +1111,10 @@
         <v>37</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>4.8</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -1140,10 +1140,10 @@
         <v>50</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -1169,10 +1169,10 @@
         <v>42</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>2</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
@@ -1198,10 +1198,10 @@
         <v>28</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>2.7</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="26" ht="26" customHeight="1">
@@ -1214,10 +1214,10 @@
       <c r="C26" s="13" t="n"/>
       <c r="D26" s="13" t="n"/>
       <c r="E26" s="14" t="n">
-        <v>875</v>
+        <v>868</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>400</v>
+        <v>382</v>
       </c>
       <c r="G26" s="15" t="n">
         <v>2.5</v>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -553,7 +553,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 12/10/2026 15:55 | Nguồn: classroom.khanacademy.org</t>
+          <t>Thời gian thống kê: 12/10/2026 16:28 | Nguồn: classroom.khanacademy.org</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -553,7 +553,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 12/10/2026 16:28 | Nguồn: classroom.khanacademy.org</t>
+          <t>Thời gian thống kê: 13/10/2026 08:34 | Nguồn: classroom.khanacademy.org</t>
         </is>
       </c>
     </row>
@@ -618,10 +618,10 @@
         <v>44</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>5.8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -647,7 +647,7 @@
         <v>47</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G6" s="11" t="n">
         <v>0.4</v>
@@ -705,10 +705,10 @@
         <v>44</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -734,10 +734,10 @@
         <v>47</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -763,10 +763,10 @@
         <v>44</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -850,10 +850,10 @@
         <v>35</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -879,10 +879,10 @@
         <v>40</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>5.3</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -937,10 +937,10 @@
         <v>46</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>9.9</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -995,10 +995,10 @@
         <v>37</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -1024,10 +1024,10 @@
         <v>35</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -1053,10 +1053,10 @@
         <v>44</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>2.2</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -1082,7 +1082,7 @@
         <v>40</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G21" s="7" t="n">
         <v>1.3</v>
@@ -1114,7 +1114,7 @@
         <v>36</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>6.9</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -1140,10 +1140,10 @@
         <v>50</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -1198,7 +1198,7 @@
         <v>28</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G25" s="7" t="n">
         <v>0.1</v>
@@ -1217,10 +1217,10 @@
         <v>868</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>382</v>
+        <v>351</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
     </row>
   </sheetData>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -16,8 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="4">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,8 +45,17 @@
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -57,8 +68,20 @@
         <bgColor rgb="001B365D"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4F8FC"/>
+        <bgColor rgb="00F4F8FC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EBF2FA"/>
+        <bgColor rgb="00EBF2FA"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -80,11 +103,25 @@
         <color rgb="00D3D3D3"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D3D3D3"/>
+      </right>
+      <top style="thin">
+        <color rgb="001B365D"/>
+      </top>
+      <bottom style="double">
+        <color rgb="001B365D"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -94,6 +131,40 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -460,7 +531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -482,7 +553,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 13/10/2026 23:26 | Nguồn: classroom.khanacademy.org</t>
+          <t>Thời gian thống kê: 14/10/2026 11:00 | Nguồn: classroom.khanacademy.org</t>
         </is>
       </c>
     </row>
@@ -524,8 +595,637 @@
         </is>
       </c>
     </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>GC65CJ23</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>10A1_Năm học 2026-2027_Nguyễn Thị Yến Linh</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Toán 10</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>44</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="G5" s="7" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>H4S4C7P2</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>10A2_Năm học 2026-2027_Trần Minh Mẫn</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Toán 10</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>47</v>
+      </c>
+      <c r="F6" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="G6" s="11" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>UWTVBASW</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>10A3_Năm học 2026-2027_Văn Thị Bích Thùy</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Toán 10</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="G7" s="7" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>FHGUSN4Z</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>10A4_Năm học 2026-2027_Văn Thị Bích Thùy</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Toán 10</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="F8" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="G8" s="11" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>4NH4T2A4</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>10A5_Năm học 2026-2027_Nguyễn Ngọc Thịnh</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Toán 10</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>47</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="G9" s="7" t="n">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>VZQP4YAF</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>10A6_Năm học 2026-2027_Nguyễn Ngọc Thịnh</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Toán 10</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="F10" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="G10" s="11" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>KMR6W4FR</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>10A7_Năm học 2026-2027_Nguyễn Chí Huy</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Toán 10</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G11" s="7" t="n">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>DZWFS5NS</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>10A8_Năm học 2026-2027_Nguyễn Thành Thái</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>Toán 10</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="F12" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="G12" s="11" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>PJP8ZHQ5</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>11A1_Năm học 2026-2027_Nguyễn Ngọc Thịnh</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Toán 11</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G13" s="7" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>UQ77Z4F8</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>11A2_Năm học 2026-2027_Nguyễn Thị Yến Linh</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>Toán 11</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="F14" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="G14" s="11" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>6JZUDEYH</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>11A3_Năm Học 2026-2027_Mai Thành Công</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Toán 11</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>44</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="G15" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>NFPJ3YUZ</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>11A4_Năm học 2026-2027_Nguyễn Thị Yến Linh</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>Toán 11</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>46</v>
+      </c>
+      <c r="F16" s="10" t="n">
+        <v>32</v>
+      </c>
+      <c r="G16" s="11" t="n">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>EJ5JBTPM</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>11A5_ Năm Học 2026-2027_Nguyễn Ngọc Thịnh</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Toán 11</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="G17" s="7" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>N6D6F43M</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>11A6_Năm học 2026-2027_Mai Thành Công</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>Toán 11</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="F18" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="G18" s="11" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Y4KXVHFH</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>12A1-Năm học 2026-2027_Trần Thị Bội Nhung</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Toán 12</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="G19" s="7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>7B39B8FY</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>12A2 - Năm học 2026-2027_Nguyễn Thành Thái</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>Toán 12</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="F20" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="G20" s="11" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>2DXNAW8H</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>12A3-Năm học 2026-2027_Mai Thành Công</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Toán 12</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="G21" s="7" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>2T2BZU9H</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>12A4-Năm học 2026-2027_Nguyễn Thành Thái</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>Toán 12</t>
+        </is>
+      </c>
+      <c r="E22" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="F22" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="G22" s="11" t="n">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>MF9R2SND</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>12A5 - Năm học 2026-2027_Trần Thị Bội Nhung</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>Toán 12</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G23" s="7" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>BQKUESU3</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>12A6 _Năm học 2026-2027_Nguyễn Thành Thái</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>Toán 12</t>
+        </is>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="F24" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="G24" s="11" t="n">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Q96EYDVA</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>12A7 - Năm học 2026 - 2027_Trần Thị Bội Nhung</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>Toán 12</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G25" s="7" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="26" ht="26" customHeight="1">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>TỔNG CỘNG / TRUNG BÌNH TOÀN BỘ:</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="n"/>
+      <c r="C26" s="13" t="n"/>
+      <c r="D26" s="13" t="n"/>
+      <c r="E26" s="14" t="n">
+        <v>868</v>
+      </c>
+      <c r="F26" s="14" t="n">
+        <v>345</v>
+      </c>
+      <c r="G26" s="15" t="n">
+        <v>2.1</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
+    <mergeCell ref="A26:D26"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -553,7 +553,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 14/10/2026 11:00 | Nguồn: classroom.khanacademy.org</t>
+          <t>Thời gian thống kê: 14/10/2026 21:22 | Nguồn: classroom.khanacademy.org</t>
         </is>
       </c>
     </row>
@@ -734,10 +734,10 @@
         <v>47</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -763,10 +763,10 @@
         <v>44</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -795,7 +795,7 @@
         <v>10</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -850,10 +850,10 @@
         <v>35</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -1140,10 +1140,10 @@
         <v>50</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -1217,10 +1217,10 @@
         <v>868</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>345</v>
+        <v>359</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
     </row>
   </sheetData>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -553,7 +553,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 14/10/2026 21:22 | Nguồn: classroom.khanacademy.org</t>
+          <t>Thời gian thống kê: 15/10/2026 14:21 | Nguồn: classroom.khanacademy.org</t>
         </is>
       </c>
     </row>
@@ -618,10 +618,10 @@
         <v>44</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -676,10 +676,10 @@
         <v>46</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -708,7 +708,7 @@
         <v>5</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -737,7 +737,7 @@
         <v>23</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -763,7 +763,7 @@
         <v>44</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G10" s="11" t="n">
         <v>3.9</v>
@@ -792,10 +792,10 @@
         <v>40</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -908,7 +908,7 @@
         <v>44</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G15" s="7" t="n">
         <v>1</v>
@@ -937,10 +937,10 @@
         <v>46</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>7.6</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -969,7 +969,7 @@
         <v>7</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -998,7 +998,7 @@
         <v>20</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -1024,7 +1024,7 @@
         <v>35</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G19" s="7" t="n">
         <v>2</v>
@@ -1082,7 +1082,7 @@
         <v>40</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G21" s="7" t="n">
         <v>0.3</v>
@@ -1140,10 +1140,10 @@
         <v>50</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -1217,10 +1217,10 @@
         <v>868</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
     </row>
   </sheetData>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -553,7 +553,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 15/10/2026 14:21 | Nguồn: classroom.khanacademy.org</t>
+          <t>Thời gian thống kê: 17/10/2026 12:14 | Nguồn: classroom.khanacademy.org</t>
         </is>
       </c>
     </row>
@@ -618,10 +618,10 @@
         <v>44</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -647,10 +647,10 @@
         <v>47</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -676,10 +676,10 @@
         <v>46</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -705,10 +705,10 @@
         <v>44</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -763,10 +763,10 @@
         <v>44</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -789,13 +789,13 @@
         </is>
       </c>
       <c r="E11" s="6" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>1.7</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -824,7 +824,7 @@
         <v>21</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -879,7 +879,7 @@
         <v>40</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G14" s="11" t="n">
         <v>0.8</v>
@@ -908,10 +908,10 @@
         <v>44</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -934,13 +934,13 @@
         </is>
       </c>
       <c r="E16" s="10" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>7.1</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -966,7 +966,7 @@
         <v>33</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G17" s="7" t="n">
         <v>0.8</v>
@@ -995,10 +995,10 @@
         <v>37</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -1024,10 +1024,10 @@
         <v>35</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -1056,7 +1056,7 @@
         <v>37</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -1082,7 +1082,7 @@
         <v>40</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G21" s="7" t="n">
         <v>0.3</v>
@@ -1111,10 +1111,10 @@
         <v>37</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>7.2</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -1140,10 +1140,10 @@
         <v>50</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -1172,7 +1172,7 @@
         <v>36</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
@@ -1198,7 +1198,7 @@
         <v>28</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G25" s="7" t="n">
         <v>0.5</v>
@@ -1214,13 +1214,13 @@
       <c r="C26" s="13" t="n"/>
       <c r="D26" s="13" t="n"/>
       <c r="E26" s="14" t="n">
-        <v>868</v>
+        <v>865</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>352</v>
+        <v>371</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
     </row>
   </sheetData>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -553,7 +553,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 17/10/2026 12:14 | Nguồn: classroom.khanacademy.org</t>
+          <t>Thời gian thống kê: 17/10/2026 12:17 | Nguồn: classroom.khanacademy.org</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -553,7 +553,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 17/10/2026 12:17 | Nguồn: classroom.khanacademy.org</t>
+          <t>Thời gian thống kê: 17/10/2026 22:34 | Nguồn: classroom.khanacademy.org</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
         <v>7</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -821,10 +821,10 @@
         <v>45</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -853,7 +853,7 @@
         <v>6</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -879,10 +879,10 @@
         <v>40</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -911,7 +911,7 @@
         <v>9</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -937,10 +937,10 @@
         <v>44</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -1024,10 +1024,10 @@
         <v>35</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -1085,7 +1085,7 @@
         <v>11</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
@@ -1140,10 +1140,10 @@
         <v>50</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -1198,10 +1198,10 @@
         <v>28</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="26" ht="26" customHeight="1">
@@ -1217,10 +1217,10 @@
         <v>865</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>371</v>
+        <v>384</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
     </row>
   </sheetData>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -553,7 +553,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 17/10/2026 22:34 | Nguồn: classroom.khanacademy.org</t>
+          <t>Thời gian thống kê: 17/10/2026 22:46 | Nguồn: classroom.khanacademy.org</t>
         </is>
       </c>
     </row>
@@ -940,7 +940,7 @@
         <v>36</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -7,7 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Báo Cáo KAV" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tổng Hợp Toàn Trường" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Khối THPT (21 lớp)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Khối THCS (12 lớp)" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -31,13 +33,13 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="001B365D"/>
-      <sz val="16"/>
+      <sz val="15"/>
     </font>
     <font>
       <name val="Calibri"/>
       <i val="1"/>
       <color rgb="00555555"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -531,6 +533,1234 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>BÁO CÁO THỐNG KÊ TOÀN TRƯỜNG KHAN ACADEMY (KAV)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Thời gian thống kê: 17/10/2026 23:04 | Trường: THCS&amp;THPT MONG THỌ</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>STT</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Khối / Phân Loại</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Mã Lớp</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Tên Lớp Học</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Khóa Học</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Số tài khoản đã tạo</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Đang hoạt động</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Kỹ Năng TB Thành Thạo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Khối THPT</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>GC65CJ23</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>10A1_Năm học 2026-2027_Nguyễn Thị Yến Linh</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Toán 10</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>44</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="H5" s="7" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Khối THPT</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>H4S4C7P2</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>10A2_Năm học 2026-2027_Trần Minh Mẫn</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>Toán 10</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="n">
+        <v>47</v>
+      </c>
+      <c r="G6" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="H6" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Khối THPT</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>UWTVBASW</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>10A3_Năm học 2026-2027_Văn Thị Bích Thùy</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Toán 10</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="H7" s="7" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Khối THPT</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>FHGUSN4Z</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>10A4_Năm học 2026-2027_Văn Thị Bích Thùy</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>Toán 10</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="G8" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Khối THPT</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>4NH4T2A4</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>10A5_Năm học 2026-2027_Nguyễn Ngọc Thịnh</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Toán 10</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>47</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="H9" s="7" t="n">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Khối THPT</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>VZQP4YAF</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>10A6_Năm học 2026-2027_Nguyễn Ngọc Thịnh</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>Toán 10</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="G10" s="10" t="n">
+        <v>22</v>
+      </c>
+      <c r="H10" s="11" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Khối THPT</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>KMR6W4FR</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>10A7_Năm học 2026-2027_Nguyễn Chí Huy</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Toán 10</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>39</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="H11" s="7" t="n">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Khối THPT</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>DZWFS5NS</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>10A8_Năm học 2026-2027_Nguyễn Thành Thái</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>Toán 10</t>
+        </is>
+      </c>
+      <c r="F12" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="G12" s="10" t="n">
+        <v>22</v>
+      </c>
+      <c r="H12" s="11" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Khối THPT</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>PJP8ZHQ5</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>11A1_Năm học 2026-2027_Nguyễn Ngọc Thịnh</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Toán 11</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="H13" s="7" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>Khối THPT</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>UQ77Z4F8</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>11A2_Năm học 2026-2027_Nguyễn Thị Yến Linh</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>Toán 11</t>
+        </is>
+      </c>
+      <c r="F14" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="G14" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="H14" s="11" t="n">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Khối THPT</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>6JZUDEYH</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>11A3_Năm Học 2026-2027_Mai Thành Công</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Toán 11</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>44</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H15" s="7" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Khối THPT</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>NFPJ3YUZ</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>11A4_Năm học 2026-2027_Nguyễn Thị Yến Linh</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>Toán 11</t>
+        </is>
+      </c>
+      <c r="F16" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="G16" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="H16" s="11" t="n">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Khối THPT</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>EJ5JBTPM</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>11A5_ Năm Học 2026-2027_Nguyễn Ngọc Thịnh</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Toán 11</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="H17" s="7" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>Khối THPT</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>N6D6F43M</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>11A6_Năm học 2026-2027_Mai Thành Công</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>Toán 11</t>
+        </is>
+      </c>
+      <c r="F18" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="G18" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="H18" s="11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Khối THPT</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Y4KXVHFH</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>12A1-Năm học 2026-2027_Trần Thị Bội Nhung</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Toán 12</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="H19" s="7" t="n">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>Khối THPT</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>7B39B8FY</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>12A2 - Năm học 2026-2027_Nguyễn Thành Thái</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>Toán 12</t>
+        </is>
+      </c>
+      <c r="F20" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="G20" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="H20" s="11" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Khối THPT</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>2DXNAW8H</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>12A3-Năm học 2026-2027_Mai Thành Công</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Toán 12</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="H21" s="7" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>Khối THPT</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>2T2BZU9H</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>12A4-Năm học 2026-2027_Nguyễn Thành Thái</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>Toán 12</t>
+        </is>
+      </c>
+      <c r="F22" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="G22" s="10" t="n">
+        <v>35</v>
+      </c>
+      <c r="H22" s="11" t="n">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Khối THPT</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>MF9R2SND</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>12A5 - Năm học 2026-2027_Trần Thị Bội Nhung</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Toán 12</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="H23" s="7" t="n">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>Khối THPT</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>BQKUESU3</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>12A6 _Năm học 2026-2027_Nguyễn Thành Thái</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>Toán 12</t>
+        </is>
+      </c>
+      <c r="F24" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="G24" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="H24" s="11" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Khối THPT</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Q96EYDVA</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>12A7 - Năm học 2026 - 2027_Trần Thị Bội Nhung</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Toán 12</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="H25" s="7" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>Khối THCS</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>THCS-6A1</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>6A1_Năm học 2026–2027_Lư Ngọc Cẩm</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>Toán 6</t>
+        </is>
+      </c>
+      <c r="F26" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="G26" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="H26" s="11" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Khối THCS</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>THCS-6A2</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>6A2_Năm học: 2026–2027_Trần Thị Lý</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>Toán 6</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>44</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="H27" s="7" t="n">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>Khối THCS</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>THCS-6A3</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>6A3_Năm học: 2026–2027_Trần Thị Lý</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>Toán 6</t>
+        </is>
+      </c>
+      <c r="F28" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="G28" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="H28" s="11" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Khối THCS</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>THCS-7A1</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>7A1– Đỗ Thị Kim Mai–2026–2027</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>Toán 7</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="G29" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H29" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>Khối THCS</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>THCS-7A2</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>7A2– 2026–2027– Nguyễn Thị Mỹ Trinh</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>Toán 7</t>
+        </is>
+      </c>
+      <c r="F30" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="G30" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="H30" s="11" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Khối THCS</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>THCS-7A3</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>7A3– 2026–2027– Nguyễn Thị Mỹ Trinh</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>Toán 7</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>44</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="H31" s="7" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>Khối THCS</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>THCS-7A4</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>7A4– 2026–2027– Nguyễn Thị Mỹ Trinh</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>Toán 7</t>
+        </is>
+      </c>
+      <c r="F32" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="G32" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="H32" s="11" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Khối THCS</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>THCS-8A1</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>8A1– 2026–2027– Nguyễn Thị Thìn</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>Toán 8</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>47</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="H33" s="7" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>Khối THCS</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>THCS-8A2</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>8A2–Đỗ Thị Kim Mai–2026–2027</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>Toán 8</t>
+        </is>
+      </c>
+      <c r="F34" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="G34" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="H34" s="11" t="n">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Khối THCS</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>THCS-8A3</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>8A3–Đỗ Thị Kim Mai–2026–2027</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>Toán 8</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="n">
+        <v>52</v>
+      </c>
+      <c r="G35" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H35" s="7" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>Khối THCS</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>THCS-9A1</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>9A1– 2026–2027–Nguyễn Thị Thìn</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t>Toán 9</t>
+        </is>
+      </c>
+      <c r="F36" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="G36" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="H36" s="11" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Khối THCS</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>THCS-9A2</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>9A2–2026–2027–Nguyễn Thị Thìn</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>Toán 9</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="n">
+        <v>47</v>
+      </c>
+      <c r="G37" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="H37" s="7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" ht="26" customHeight="1">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>TỔNG CỘNG / TRUNG BÌNH:</t>
+        </is>
+      </c>
+      <c r="B38" s="13" t="n"/>
+      <c r="C38" s="13" t="n"/>
+      <c r="D38" s="13" t="n"/>
+      <c r="E38" s="13" t="n"/>
+      <c r="F38" s="14" t="n">
+        <v>1424</v>
+      </c>
+      <c r="G38" s="14" t="n">
+        <v>530</v>
+      </c>
+      <c r="H38" s="15" t="n">
+        <v>2.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -543,22 +1773,22 @@
     <col width="24" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BÁO CÁO THỐNG KÊ KỸ NĂNG THÀNH THẠO KHAN ACADEMY (KAV)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
+          <t>BÁO CÁO KỸ NĂNG THÀNH THẠO KHỐI THPT (TOÁN 10 - 11 - 12)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 17/10/2026 22:46 | Nguồn: classroom.khanacademy.org</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="10" customHeight="1"/>
-    <row r="4" ht="28" customHeight="1">
+          <t>Thời gian thống kê: 17/10/2026 23:04 | Trường: THCS&amp;THPT MONG THỌ</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="26" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>STT</t>
@@ -1207,7 +2437,7 @@
     <row r="26" ht="26" customHeight="1">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>TỔNG CỘNG / TRUNG BÌNH TOÀN BỘ:</t>
+          <t>TỔNG CỘNG / TRUNG BÌNH:</t>
         </is>
       </c>
       <c r="B26" s="13" t="n"/>
@@ -1231,4 +2461,451 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>BÁO CÁO KỸ NĂNG THÀNH THẠO KHỐI THCS (TOÁN 6 - 7 - 8 - 9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Thời gian thống kê: 17/10/2026 23:04 | Trường: THCS&amp;THPT MONG THỌ</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>STT</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Mã Lớp</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Tên Lớp Học</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Khóa Học / Môn</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Số tài khoản đã tạo</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Số tài khoản đang hoạt động</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Kỹ Năng TB Thành Thạo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>THCS-6A1</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>6A1_Năm học 2026–2027_Lư Ngọc Cẩm</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Toán 6</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>44</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="G5" s="7" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>THCS-6A2</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>6A2_Năm học: 2026–2027_Trần Thị Lý</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Toán 6</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="F6" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="G6" s="11" t="n">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>THCS-6A3</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>6A3_Năm học: 2026–2027_Trần Thị Lý</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Toán 6</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="G7" s="7" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>THCS-7A1</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>7A1– Đỗ Thị Kim Mai–2026–2027</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Toán 7</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>43</v>
+      </c>
+      <c r="F8" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>THCS-7A2</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>7A2– 2026–2027– Nguyễn Thị Mỹ Trinh</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Toán 7</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="G9" s="7" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>THCS-7A3</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>7A3– 2026–2027– Nguyễn Thị Mỹ Trinh</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Toán 7</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="F10" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="G10" s="11" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>THCS-7A4</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>7A4– 2026–2027– Nguyễn Thị Mỹ Trinh</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Toán 7</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G11" s="7" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>THCS-8A1</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>8A1– 2026–2027– Nguyễn Thị Thìn</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>Toán 8</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>47</v>
+      </c>
+      <c r="F12" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="G12" s="11" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>THCS-8A2</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>8A2–Đỗ Thị Kim Mai–2026–2027</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Toán 8</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>55</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="G13" s="7" t="n">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>THCS-8A3</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>8A3–Đỗ Thị Kim Mai–2026–2027</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>Toán 8</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="n">
+        <v>52</v>
+      </c>
+      <c r="F14" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="G14" s="11" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>THCS-9A1</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>9A1– 2026–2027–Nguyễn Thị Thìn</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Toán 9</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="G15" s="7" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>THCS-9A2</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>9A2–2026–2027–Nguyễn Thị Thìn</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>Toán 9</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>47</v>
+      </c>
+      <c r="F16" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="G16" s="11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" ht="26" customHeight="1">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>TỔNG CỘNG / TRUNG BÌNH:</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="n"/>
+      <c r="C17" s="13" t="n"/>
+      <c r="D17" s="13" t="n"/>
+      <c r="E17" s="14" t="n">
+        <v>559</v>
+      </c>
+      <c r="F17" s="14" t="n">
+        <v>146</v>
+      </c>
+      <c r="G17" s="15" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 17/10/2026 23:04 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 17/10/2026 23:05 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1783,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 17/10/2026 23:04 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 17/10/2026 23:05 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -2491,7 +2491,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 17/10/2026 23:04 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 17/10/2026 23:05 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tổng Hợp Toàn Trường" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Khối THPT (21 lớp)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Khối THCS (12 lớp)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Khối THCS (13 lớp)" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -533,7 +533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 17/10/2026 23:05 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 17/10/2026 23:13 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -1725,29 +1725,63 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" ht="26" customHeight="1">
-      <c r="A38" s="12" t="inlineStr">
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="8" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>Khối THCS</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>THCS-9A3</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>9A3 – Năm học 2026–2027– Trần Thị Lý</t>
+        </is>
+      </c>
+      <c r="E38" s="8" t="inlineStr">
+        <is>
+          <t>Toán 9</t>
+        </is>
+      </c>
+      <c r="F38" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="G38" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="H38" s="11" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="39" ht="26" customHeight="1">
+      <c r="A39" s="12" t="inlineStr">
         <is>
           <t>TỔNG CỘNG / TRUNG BÌNH:</t>
         </is>
       </c>
-      <c r="B38" s="13" t="n"/>
-      <c r="C38" s="13" t="n"/>
-      <c r="D38" s="13" t="n"/>
-      <c r="E38" s="13" t="n"/>
-      <c r="F38" s="14" t="n">
-        <v>1424</v>
-      </c>
-      <c r="G38" s="14" t="n">
-        <v>530</v>
-      </c>
-      <c r="H38" s="15" t="n">
-        <v>2.1</v>
+      <c r="B39" s="13" t="n"/>
+      <c r="C39" s="13" t="n"/>
+      <c r="D39" s="13" t="n"/>
+      <c r="E39" s="13" t="n"/>
+      <c r="F39" s="14" t="n">
+        <v>1469</v>
+      </c>
+      <c r="G39" s="14" t="n">
+        <v>540</v>
+      </c>
+      <c r="H39" s="15" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="A39:E39"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
@@ -1783,7 +1817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 17/10/2026 23:05 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 17/10/2026 23:13 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -2469,7 +2503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2491,7 +2525,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 17/10/2026 23:05 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 17/10/2026 23:13 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -2881,30 +2915,59 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="12" t="inlineStr">
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>THCS-9A3</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>9A3 – Năm học 2026–2027– Trần Thị Lý</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Toán 9</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G17" s="7" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>TỔNG CỘNG / TRUNG BÌNH:</t>
         </is>
       </c>
-      <c r="B17" s="13" t="n"/>
-      <c r="C17" s="13" t="n"/>
-      <c r="D17" s="13" t="n"/>
-      <c r="E17" s="14" t="n">
-        <v>559</v>
-      </c>
-      <c r="F17" s="14" t="n">
-        <v>146</v>
-      </c>
-      <c r="G17" s="15" t="n">
-        <v>1.2</v>
+      <c r="B18" s="13" t="n"/>
+      <c r="C18" s="13" t="n"/>
+      <c r="D18" s="13" t="n"/>
+      <c r="E18" s="14" t="n">
+        <v>604</v>
+      </c>
+      <c r="F18" s="14" t="n">
+        <v>156</v>
+      </c>
+      <c r="G18" s="15" t="n">
+        <v>1.1</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A17:D17"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A18:D18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 17/10/2026 23:13 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 17/10/2026 23:22 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
         <v>22</v>
       </c>
       <c r="H12" s="11" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -1073,10 +1073,10 @@
         <v>37</v>
       </c>
       <c r="G18" s="10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H18" s="11" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -1773,10 +1773,10 @@
         <v>1469</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
     </row>
   </sheetData>
@@ -1817,7 +1817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 17/10/2026 23:13 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 17/10/2026 23:22 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
         <v>22</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -2259,10 +2259,10 @@
         <v>37</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -2481,7 +2481,7 @@
         <v>865</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="G26" s="15" t="n">
         <v>2.6</v>
@@ -2525,7 +2525,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 17/10/2026 23:13 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 17/10/2026 23:22 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 17/10/2026 23:22 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 17/10/2026 23:23 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -1817,7 +1817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 17/10/2026 23:22 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 17/10/2026 23:23 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 17/10/2026 23:22 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 17/10/2026 23:23 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 17/10/2026 23:23 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 18/10/2026 07:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -699,10 +699,10 @@
         <v>46</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -767,10 +767,10 @@
         <v>47</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -804,7 +804,7 @@
         <v>22</v>
       </c>
       <c r="H10" s="11" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -838,7 +838,7 @@
         <v>30</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>9.6</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -869,10 +869,10 @@
         <v>45</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H12" s="11" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -937,10 +937,10 @@
         <v>40</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H14" s="11" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -971,10 +971,10 @@
         <v>44</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -1005,10 +1005,10 @@
         <v>44</v>
       </c>
       <c r="G16" s="10" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H16" s="11" t="n">
-        <v>7.7</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -1039,10 +1039,10 @@
         <v>33</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -1073,10 +1073,10 @@
         <v>37</v>
       </c>
       <c r="G18" s="10" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H18" s="11" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -1107,10 +1107,10 @@
         <v>35</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -1144,7 +1144,7 @@
         <v>37</v>
       </c>
       <c r="H20" s="11" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -1175,7 +1175,7 @@
         <v>40</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H21" s="7" t="n">
         <v>0.7</v>
@@ -1209,10 +1209,10 @@
         <v>37</v>
       </c>
       <c r="G22" s="10" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="H22" s="11" t="n">
-        <v>6.9</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -1243,10 +1243,10 @@
         <v>50</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H23" s="7" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -1277,10 +1277,10 @@
         <v>42</v>
       </c>
       <c r="G24" s="10" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="H24" s="11" t="n">
-        <v>3.7</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
@@ -1773,10 +1773,10 @@
         <v>1469</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>541</v>
+        <v>499</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
     </row>
   </sheetData>
@@ -1817,7 +1817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 17/10/2026 23:23 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 18/10/2026 07:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -1940,10 +1940,10 @@
         <v>46</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -1998,10 +1998,10 @@
         <v>47</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -2030,7 +2030,7 @@
         <v>22</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -2059,7 +2059,7 @@
         <v>30</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>9.6</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -2085,10 +2085,10 @@
         <v>45</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -2143,10 +2143,10 @@
         <v>40</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -2172,10 +2172,10 @@
         <v>44</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -2201,10 +2201,10 @@
         <v>44</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>7.7</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -2230,10 +2230,10 @@
         <v>33</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -2259,10 +2259,10 @@
         <v>37</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -2288,10 +2288,10 @@
         <v>35</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -2320,7 +2320,7 @@
         <v>37</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -2346,7 +2346,7 @@
         <v>40</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G21" s="7" t="n">
         <v>0.7</v>
@@ -2375,10 +2375,10 @@
         <v>37</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>6.9</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -2404,10 +2404,10 @@
         <v>50</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -2433,10 +2433,10 @@
         <v>42</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>3.7</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
@@ -2481,10 +2481,10 @@
         <v>865</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>385</v>
+        <v>343</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
     </row>
   </sheetData>
@@ -2525,7 +2525,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 17/10/2026 23:23 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 18/10/2026 07:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 18/10/2026 07:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 18/10/2026 08:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
         <v>34</v>
       </c>
       <c r="H16" s="11" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -1042,7 +1042,7 @@
         <v>9</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -1175,10 +1175,10 @@
         <v>40</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
@@ -1311,7 +1311,7 @@
         <v>28</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H25" s="7" t="n">
         <v>0.8</v>
@@ -1773,7 +1773,7 @@
         <v>1469</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="H39" s="15" t="n">
         <v>1.8</v>
@@ -1817,7 +1817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 18/10/2026 07:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 18/10/2026 08:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
         <v>34</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -2233,7 +2233,7 @@
         <v>9</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -2346,10 +2346,10 @@
         <v>40</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
@@ -2462,7 +2462,7 @@
         <v>28</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G25" s="7" t="n">
         <v>0.8</v>
@@ -2481,10 +2481,10 @@
         <v>865</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
     </row>
   </sheetData>
@@ -2525,7 +2525,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 18/10/2026 07:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 18/10/2026 08:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 18/10/2026 08:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 18/10/2026 09:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -1005,7 +1005,7 @@
         <v>44</v>
       </c>
       <c r="G16" s="10" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H16" s="11" t="n">
         <v>6.9</v>
@@ -1773,7 +1773,7 @@
         <v>1469</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H39" s="15" t="n">
         <v>1.8</v>
@@ -1817,7 +1817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 18/10/2026 08:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 18/10/2026 09:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -2201,7 +2201,7 @@
         <v>44</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G16" s="11" t="n">
         <v>6.9</v>
@@ -2481,7 +2481,7 @@
         <v>865</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G26" s="15" t="n">
         <v>2.2</v>
@@ -2525,7 +2525,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 18/10/2026 08:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 18/10/2026 09:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 18/10/2026 09:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 18/10/2026 13:23 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -699,10 +699,10 @@
         <v>46</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -733,10 +733,10 @@
         <v>44</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H8" s="11" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -937,10 +937,10 @@
         <v>40</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H14" s="11" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -971,10 +971,10 @@
         <v>44</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -1008,7 +1008,7 @@
         <v>35</v>
       </c>
       <c r="H16" s="11" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -1039,10 +1039,10 @@
         <v>33</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -1175,10 +1175,10 @@
         <v>40</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
@@ -1243,10 +1243,10 @@
         <v>50</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H23" s="7" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -1773,7 +1773,7 @@
         <v>1469</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>502</v>
+        <v>520</v>
       </c>
       <c r="H39" s="15" t="n">
         <v>1.8</v>
@@ -1817,7 +1817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 18/10/2026 09:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 18/10/2026 13:23 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -1940,10 +1940,10 @@
         <v>46</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -1969,10 +1969,10 @@
         <v>44</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -2143,10 +2143,10 @@
         <v>40</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -2172,10 +2172,10 @@
         <v>44</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -2204,7 +2204,7 @@
         <v>35</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -2230,10 +2230,10 @@
         <v>33</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -2346,10 +2346,10 @@
         <v>40</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
@@ -2404,10 +2404,10 @@
         <v>50</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -2481,7 +2481,7 @@
         <v>865</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>346</v>
+        <v>364</v>
       </c>
       <c r="G26" s="15" t="n">
         <v>2.2</v>
@@ -2525,7 +2525,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 18/10/2026 09:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 18/10/2026 13:23 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 18/10/2026 13:23 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 19/10/2026 07:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -631,10 +631,10 @@
         <v>44</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -665,7 +665,7 @@
         <v>47</v>
       </c>
       <c r="G6" s="10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H6" s="11" t="n">
         <v>0</v>
@@ -699,10 +699,10 @@
         <v>46</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -733,10 +733,10 @@
         <v>44</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="H8" s="11" t="n">
-        <v>0.1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -767,10 +767,10 @@
         <v>47</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -801,10 +801,10 @@
         <v>44</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H10" s="11" t="n">
-        <v>2.9</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -838,7 +838,7 @@
         <v>30</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -872,7 +872,7 @@
         <v>21</v>
       </c>
       <c r="H12" s="11" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -903,10 +903,10 @@
         <v>35</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -937,10 +937,10 @@
         <v>40</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="H14" s="11" t="n">
-        <v>2.4</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -971,10 +971,10 @@
         <v>44</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>1.4</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -1008,7 +1008,7 @@
         <v>35</v>
       </c>
       <c r="H16" s="11" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -1039,10 +1039,10 @@
         <v>33</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -1073,10 +1073,10 @@
         <v>37</v>
       </c>
       <c r="G18" s="10" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="H18" s="11" t="n">
-        <v>1.3</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -1107,10 +1107,10 @@
         <v>35</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -1141,10 +1141,10 @@
         <v>44</v>
       </c>
       <c r="G20" s="10" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="H20" s="11" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -1175,10 +1175,10 @@
         <v>40</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>0.9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
@@ -1209,10 +1209,10 @@
         <v>37</v>
       </c>
       <c r="G22" s="10" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="H22" s="11" t="n">
-        <v>2.1</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="F23" s="6" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="H23" s="7" t="n">
-        <v>2</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -1277,10 +1277,10 @@
         <v>42</v>
       </c>
       <c r="G24" s="10" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="H24" s="11" t="n">
-        <v>2.3</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
@@ -1311,10 +1311,10 @@
         <v>28</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H25" s="7" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1">
@@ -1770,13 +1770,13 @@
       <c r="D39" s="13" t="n"/>
       <c r="E39" s="13" t="n"/>
       <c r="F39" s="14" t="n">
-        <v>1469</v>
+        <v>1464</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -1817,7 +1817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 18/10/2026 13:23 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 19/10/2026 07:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -1882,10 +1882,10 @@
         <v>44</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -1911,7 +1911,7 @@
         <v>47</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G6" s="11" t="n">
         <v>0</v>
@@ -1940,10 +1940,10 @@
         <v>46</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -1969,10 +1969,10 @@
         <v>44</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>0.1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -1998,10 +1998,10 @@
         <v>47</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -2027,10 +2027,10 @@
         <v>44</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>2.9</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -2059,7 +2059,7 @@
         <v>30</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -2088,7 +2088,7 @@
         <v>21</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -2114,10 +2114,10 @@
         <v>35</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -2143,10 +2143,10 @@
         <v>40</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>2.4</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -2172,10 +2172,10 @@
         <v>44</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>1.4</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -2204,7 +2204,7 @@
         <v>35</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -2230,10 +2230,10 @@
         <v>33</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -2259,10 +2259,10 @@
         <v>37</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>1.3</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -2288,10 +2288,10 @@
         <v>35</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -2317,10 +2317,10 @@
         <v>44</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -2346,10 +2346,10 @@
         <v>40</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>0.9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
@@ -2375,10 +2375,10 @@
         <v>37</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>2.1</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -2401,13 +2401,13 @@
         </is>
       </c>
       <c r="E23" s="6" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>2</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -2433,10 +2433,10 @@
         <v>42</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>2.3</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
@@ -2462,10 +2462,10 @@
         <v>28</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="26" ht="26" customHeight="1">
@@ -2478,13 +2478,13 @@
       <c r="C26" s="13" t="n"/>
       <c r="D26" s="13" t="n"/>
       <c r="E26" s="14" t="n">
-        <v>865</v>
+        <v>860</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>364</v>
+        <v>376</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
     </row>
   </sheetData>
@@ -2525,7 +2525,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 18/10/2026 13:23 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 19/10/2026 07:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 19/10/2026 07:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 19/10/2026 08:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -733,7 +733,7 @@
         <v>44</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H8" s="11" t="n">
         <v>1.2</v>
@@ -1178,7 +1178,7 @@
         <v>20</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
@@ -1773,7 +1773,7 @@
         <v>1464</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H39" s="15" t="n">
         <v>2</v>
@@ -1817,7 +1817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 19/10/2026 07:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 19/10/2026 08:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -1969,7 +1969,7 @@
         <v>44</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G8" s="11" t="n">
         <v>1.2</v>
@@ -2349,7 +2349,7 @@
         <v>20</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
@@ -2481,7 +2481,7 @@
         <v>860</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="G26" s="15" t="n">
         <v>2.6</v>
@@ -2525,7 +2525,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 19/10/2026 07:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 19/10/2026 08:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 19/10/2026 08:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 19/10/2026 11:00 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
         <v>46</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H7" s="7" t="n">
         <v>0.9</v>
@@ -1773,7 +1773,7 @@
         <v>1464</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H39" s="15" t="n">
         <v>2</v>
@@ -1817,7 +1817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 19/10/2026 08:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 19/10/2026 11:00 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -1940,7 +1940,7 @@
         <v>46</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>0.9</v>
@@ -2481,7 +2481,7 @@
         <v>860</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="G26" s="15" t="n">
         <v>2.6</v>
@@ -2525,7 +2525,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 19/10/2026 08:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 19/10/2026 11:00 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 19/10/2026 11:00 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 20/10/2026 07:42 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -631,10 +631,10 @@
         <v>44</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -665,7 +665,7 @@
         <v>47</v>
       </c>
       <c r="G6" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H6" s="11" t="n">
         <v>0</v>
@@ -699,7 +699,7 @@
         <v>46</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H7" s="7" t="n">
         <v>0.9</v>
@@ -733,10 +733,10 @@
         <v>44</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H8" s="11" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -767,10 +767,10 @@
         <v>47</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -801,10 +801,10 @@
         <v>44</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H10" s="11" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -872,7 +872,7 @@
         <v>21</v>
       </c>
       <c r="H12" s="11" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -906,7 +906,7 @@
         <v>7</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -937,10 +937,10 @@
         <v>40</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="H14" s="11" t="n">
-        <v>5.2</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -1005,10 +1005,10 @@
         <v>44</v>
       </c>
       <c r="G16" s="10" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="H16" s="11" t="n">
-        <v>7.4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -1042,7 +1042,7 @@
         <v>9</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -1076,7 +1076,7 @@
         <v>22</v>
       </c>
       <c r="H18" s="11" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -1107,10 +1107,10 @@
         <v>35</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -1141,10 +1141,10 @@
         <v>44</v>
       </c>
       <c r="G20" s="10" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H20" s="11" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -1175,10 +1175,10 @@
         <v>40</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
@@ -1277,10 +1277,10 @@
         <v>42</v>
       </c>
       <c r="G24" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H24" s="11" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
@@ -1314,7 +1314,7 @@
         <v>10</v>
       </c>
       <c r="H25" s="7" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1">
@@ -1773,7 +1773,7 @@
         <v>1464</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="H39" s="15" t="n">
         <v>2</v>
@@ -1817,7 +1817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 19/10/2026 11:00 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 20/10/2026 07:42 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -1882,10 +1882,10 @@
         <v>44</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -1911,7 +1911,7 @@
         <v>47</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6" s="11" t="n">
         <v>0</v>
@@ -1940,7 +1940,7 @@
         <v>46</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>0.9</v>
@@ -1969,10 +1969,10 @@
         <v>44</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -1998,10 +1998,10 @@
         <v>47</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -2027,10 +2027,10 @@
         <v>44</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -2088,7 +2088,7 @@
         <v>21</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -2117,7 +2117,7 @@
         <v>7</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -2143,10 +2143,10 @@
         <v>40</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>5.2</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -2201,10 +2201,10 @@
         <v>44</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>7.4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -2233,7 +2233,7 @@
         <v>9</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -2262,7 +2262,7 @@
         <v>22</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -2288,10 +2288,10 @@
         <v>35</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -2317,10 +2317,10 @@
         <v>44</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -2346,10 +2346,10 @@
         <v>40</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
@@ -2433,10 +2433,10 @@
         <v>42</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
@@ -2465,7 +2465,7 @@
         <v>10</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="26" ht="26" customHeight="1">
@@ -2481,7 +2481,7 @@
         <v>860</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="G26" s="15" t="n">
         <v>2.6</v>
@@ -2525,7 +2525,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 19/10/2026 11:00 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 20/10/2026 07:42 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 20/10/2026 07:42 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 20/10/2026 08:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -937,10 +937,10 @@
         <v>40</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H14" s="11" t="n">
-        <v>9.199999999999999</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -1773,10 +1773,10 @@
         <v>1464</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
     </row>
   </sheetData>
@@ -1817,7 +1817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 20/10/2026 07:42 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 20/10/2026 08:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -2143,10 +2143,10 @@
         <v>40</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>9.199999999999999</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -2481,10 +2481,10 @@
         <v>860</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
     </row>
   </sheetData>
@@ -2525,7 +2525,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 20/10/2026 07:42 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 20/10/2026 08:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 20/10/2026 08:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 20/10/2026 09:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -1817,7 +1817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 20/10/2026 08:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 20/10/2026 09:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 20/10/2026 08:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 20/10/2026 09:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 20/10/2026 09:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 20/10/2026 10:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -1817,7 +1817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 20/10/2026 09:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 20/10/2026 10:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 20/10/2026 09:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 20/10/2026 10:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 20/10/2026 10:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 20/10/2026 11:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -733,7 +733,7 @@
         <v>44</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H8" s="11" t="n">
         <v>1.5</v>
@@ -1773,7 +1773,7 @@
         <v>1464</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H39" s="15" t="n">
         <v>2.1</v>
@@ -1817,7 +1817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 20/10/2026 10:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 20/10/2026 11:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -1969,7 +1969,7 @@
         <v>44</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G8" s="11" t="n">
         <v>1.5</v>
@@ -2481,7 +2481,7 @@
         <v>860</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="G26" s="15" t="n">
         <v>2.7</v>
@@ -2525,7 +2525,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 20/10/2026 10:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 20/10/2026 11:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 20/10/2026 11:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 20/10/2026 20:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -665,7 +665,7 @@
         <v>47</v>
       </c>
       <c r="G6" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H6" s="11" t="n">
         <v>0</v>
@@ -699,7 +699,7 @@
         <v>46</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H7" s="7" t="n">
         <v>0.9</v>
@@ -869,10 +869,10 @@
         <v>45</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H12" s="11" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -903,10 +903,10 @@
         <v>35</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -940,7 +940,7 @@
         <v>28</v>
       </c>
       <c r="H14" s="11" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -1005,7 +1005,7 @@
         <v>44</v>
       </c>
       <c r="G16" s="10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H16" s="11" t="n">
         <v>5</v>
@@ -1039,7 +1039,7 @@
         <v>33</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H17" s="7" t="n">
         <v>1.9</v>
@@ -1175,10 +1175,10 @@
         <v>40</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
@@ -1773,7 +1773,7 @@
         <v>1464</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>533</v>
+        <v>543</v>
       </c>
       <c r="H39" s="15" t="n">
         <v>2.1</v>
@@ -1817,7 +1817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 20/10/2026 11:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 20/10/2026 20:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -1911,7 +1911,7 @@
         <v>47</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6" s="11" t="n">
         <v>0</v>
@@ -1940,7 +1940,7 @@
         <v>46</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>0.9</v>
@@ -2085,10 +2085,10 @@
         <v>45</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -2114,10 +2114,10 @@
         <v>35</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -2146,7 +2146,7 @@
         <v>28</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -2201,7 +2201,7 @@
         <v>44</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G16" s="11" t="n">
         <v>5</v>
@@ -2230,7 +2230,7 @@
         <v>33</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G17" s="7" t="n">
         <v>1.9</v>
@@ -2346,10 +2346,10 @@
         <v>40</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
@@ -2481,7 +2481,7 @@
         <v>860</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="G26" s="15" t="n">
         <v>2.7</v>
@@ -2525,7 +2525,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 20/10/2026 11:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 20/10/2026 20:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 20/10/2026 20:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 21/10/2026 11:00 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -767,10 +767,10 @@
         <v>47</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -801,10 +801,10 @@
         <v>44</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H10" s="11" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -869,10 +869,10 @@
         <v>45</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H12" s="11" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -906,7 +906,7 @@
         <v>8</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -937,10 +937,10 @@
         <v>40</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H14" s="11" t="n">
-        <v>10.4</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -974,7 +974,7 @@
         <v>25</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -1008,7 +1008,7 @@
         <v>31</v>
       </c>
       <c r="H16" s="11" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -1073,7 +1073,7 @@
         <v>37</v>
       </c>
       <c r="G18" s="10" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H18" s="11" t="n">
         <v>3.4</v>
@@ -1107,10 +1107,10 @@
         <v>35</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -1141,10 +1141,10 @@
         <v>44</v>
       </c>
       <c r="G20" s="10" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="H20" s="11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -1209,10 +1209,10 @@
         <v>37</v>
       </c>
       <c r="G22" s="10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H22" s="11" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -1243,10 +1243,10 @@
         <v>45</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H23" s="7" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -1311,10 +1311,10 @@
         <v>28</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H25" s="7" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1">
@@ -1773,10 +1773,10 @@
         <v>1464</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>543</v>
+        <v>492</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
     </row>
   </sheetData>
@@ -1817,7 +1817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 20/10/2026 20:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 21/10/2026 11:00 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -1998,10 +1998,10 @@
         <v>47</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -2027,10 +2027,10 @@
         <v>44</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -2085,10 +2085,10 @@
         <v>45</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -2117,7 +2117,7 @@
         <v>8</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -2143,10 +2143,10 @@
         <v>40</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>10.4</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -2175,7 +2175,7 @@
         <v>25</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -2204,7 +2204,7 @@
         <v>31</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -2259,7 +2259,7 @@
         <v>37</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G18" s="11" t="n">
         <v>3.4</v>
@@ -2288,10 +2288,10 @@
         <v>35</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -2317,10 +2317,10 @@
         <v>44</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -2375,10 +2375,10 @@
         <v>37</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -2404,10 +2404,10 @@
         <v>45</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -2462,10 +2462,10 @@
         <v>28</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="26" ht="26" customHeight="1">
@@ -2481,10 +2481,10 @@
         <v>860</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>387</v>
+        <v>336</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
     </row>
   </sheetData>
@@ -2525,7 +2525,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 20/10/2026 20:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 21/10/2026 11:00 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 21/10/2026 11:00 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 21/10/2026 11:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -1817,7 +1817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 21/10/2026 11:00 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 21/10/2026 11:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 21/10/2026 11:00 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 21/10/2026 11:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 21/10/2026 11:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 21/10/2026 17:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
         <v>30</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -872,7 +872,7 @@
         <v>21</v>
       </c>
       <c r="H12" s="11" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -1039,10 +1039,10 @@
         <v>33</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -1773,10 +1773,10 @@
         <v>1464</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -1817,7 +1817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 21/10/2026 11:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 21/10/2026 17:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -2059,7 +2059,7 @@
         <v>30</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -2088,7 +2088,7 @@
         <v>21</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -2230,10 +2230,10 @@
         <v>33</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -2481,7 +2481,7 @@
         <v>860</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="G26" s="15" t="n">
         <v>2.5</v>
@@ -2525,7 +2525,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 21/10/2026 11:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 21/10/2026 17:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 21/10/2026 17:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 21/10/2026 22:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         <v>19</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -869,7 +869,7 @@
         <v>45</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H12" s="11" t="n">
         <v>2.2</v>
@@ -937,10 +937,10 @@
         <v>40</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H14" s="11" t="n">
-        <v>10.2</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -974,7 +974,7 @@
         <v>25</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -1005,7 +1005,7 @@
         <v>44</v>
       </c>
       <c r="G16" s="10" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H16" s="11" t="n">
         <v>4.8</v>
@@ -1039,7 +1039,7 @@
         <v>33</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H17" s="7" t="n">
         <v>2</v>
@@ -1178,7 +1178,7 @@
         <v>23</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
@@ -1773,7 +1773,7 @@
         <v>1464</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="H39" s="15" t="n">
         <v>2</v>
@@ -1817,7 +1817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 21/10/2026 17:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 21/10/2026 22:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -1943,7 +1943,7 @@
         <v>19</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -2085,7 +2085,7 @@
         <v>45</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G12" s="11" t="n">
         <v>2.2</v>
@@ -2143,10 +2143,10 @@
         <v>40</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>10.2</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -2175,7 +2175,7 @@
         <v>25</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -2201,7 +2201,7 @@
         <v>44</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G16" s="11" t="n">
         <v>4.8</v>
@@ -2230,7 +2230,7 @@
         <v>33</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G17" s="7" t="n">
         <v>2</v>
@@ -2349,7 +2349,7 @@
         <v>23</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
@@ -2481,7 +2481,7 @@
         <v>860</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="G26" s="15" t="n">
         <v>2.5</v>
@@ -2525,7 +2525,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 21/10/2026 17:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 21/10/2026 22:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 21/10/2026 22:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 21/10/2026 23:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -1817,7 +1817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 21/10/2026 22:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 21/10/2026 23:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 21/10/2026 22:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 21/10/2026 23:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 21/10/2026 23:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 22/10/2026 11:29 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -631,7 +631,7 @@
         <v>44</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H5" s="7" t="n">
         <v>0.6</v>
@@ -767,10 +767,10 @@
         <v>47</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -801,10 +801,10 @@
         <v>44</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H10" s="11" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -838,7 +838,7 @@
         <v>30</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>9.1</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -869,10 +869,10 @@
         <v>45</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H12" s="11" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -906,7 +906,7 @@
         <v>8</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -937,10 +937,10 @@
         <v>40</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H14" s="11" t="n">
-        <v>10.6</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -1008,7 +1008,7 @@
         <v>32</v>
       </c>
       <c r="H16" s="11" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -1073,7 +1073,7 @@
         <v>37</v>
       </c>
       <c r="G18" s="10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H18" s="11" t="n">
         <v>3.4</v>
@@ -1141,7 +1141,7 @@
         <v>44</v>
       </c>
       <c r="G20" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H20" s="11" t="n">
         <v>0</v>
@@ -1243,10 +1243,10 @@
         <v>45</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="H23" s="7" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -1773,10 +1773,10 @@
         <v>1464</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>497</v>
+        <v>473</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
     </row>
   </sheetData>
@@ -1817,7 +1817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 21/10/2026 23:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 22/10/2026 11:29 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
         <v>44</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G5" s="7" t="n">
         <v>0.6</v>
@@ -1998,10 +1998,10 @@
         <v>47</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -2027,10 +2027,10 @@
         <v>44</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -2059,7 +2059,7 @@
         <v>30</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>9.1</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -2085,10 +2085,10 @@
         <v>45</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -2117,7 +2117,7 @@
         <v>8</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -2143,10 +2143,10 @@
         <v>40</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>10.6</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -2204,7 +2204,7 @@
         <v>32</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -2259,7 +2259,7 @@
         <v>37</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G18" s="11" t="n">
         <v>3.4</v>
@@ -2317,7 +2317,7 @@
         <v>44</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G20" s="11" t="n">
         <v>0</v>
@@ -2404,10 +2404,10 @@
         <v>45</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -2481,10 +2481,10 @@
         <v>860</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>341</v>
+        <v>317</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
     </row>
   </sheetData>
@@ -2525,7 +2525,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 21/10/2026 23:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 22/10/2026 11:29 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 22/10/2026 11:29 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 22/10/2026 12:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -1817,7 +1817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 22/10/2026 11:29 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 22/10/2026 12:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 22/10/2026 11:29 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 22/10/2026 12:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 22/10/2026 12:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 22/10/2026 14:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -1817,7 +1817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 22/10/2026 12:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 22/10/2026 14:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 22/10/2026 12:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 22/10/2026 14:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 22/10/2026 14:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 22/10/2026 15:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -971,10 +971,10 @@
         <v>44</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -1773,7 +1773,7 @@
         <v>1464</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H39" s="15" t="n">
         <v>1.9</v>
@@ -1817,7 +1817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 22/10/2026 14:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 22/10/2026 15:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -2172,10 +2172,10 @@
         <v>44</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -2481,7 +2481,7 @@
         <v>860</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="G26" s="15" t="n">
         <v>2.4</v>
@@ -2525,7 +2525,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 22/10/2026 14:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 22/10/2026 15:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 22/10/2026 15:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 22/10/2026 17:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1039,7 @@
         <v>33</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H17" s="7" t="n">
         <v>2</v>
@@ -1175,10 +1175,10 @@
         <v>40</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
@@ -1773,7 +1773,7 @@
         <v>1464</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="H39" s="15" t="n">
         <v>1.9</v>
@@ -1817,7 +1817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 22/10/2026 15:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 22/10/2026 17:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -2230,7 +2230,7 @@
         <v>33</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G17" s="7" t="n">
         <v>2</v>
@@ -2346,10 +2346,10 @@
         <v>40</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
@@ -2481,7 +2481,7 @@
         <v>860</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="G26" s="15" t="n">
         <v>2.4</v>
@@ -2525,7 +2525,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 22/10/2026 15:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 22/10/2026 17:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 22/10/2026 17:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 22/10/2026 23:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         <v>19</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -733,7 +733,7 @@
         <v>44</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H8" s="11" t="n">
         <v>1.5</v>
@@ -838,7 +838,7 @@
         <v>30</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>8.9</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -903,10 +903,10 @@
         <v>35</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -1039,10 +1039,10 @@
         <v>33</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -1076,7 +1076,7 @@
         <v>19</v>
       </c>
       <c r="H18" s="11" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -1141,7 +1141,7 @@
         <v>44</v>
       </c>
       <c r="G20" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H20" s="11" t="n">
         <v>0</v>
@@ -1178,7 +1178,7 @@
         <v>24</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
@@ -1773,10 +1773,10 @@
         <v>1464</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -1817,7 +1817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 22/10/2026 17:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 22/10/2026 23:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -1943,7 +1943,7 @@
         <v>19</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -1969,7 +1969,7 @@
         <v>44</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G8" s="11" t="n">
         <v>1.5</v>
@@ -2059,7 +2059,7 @@
         <v>30</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>8.9</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -2114,10 +2114,10 @@
         <v>35</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -2230,10 +2230,10 @@
         <v>33</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -2262,7 +2262,7 @@
         <v>19</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -2317,7 +2317,7 @@
         <v>44</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G20" s="11" t="n">
         <v>0</v>
@@ -2349,7 +2349,7 @@
         <v>24</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
@@ -2481,10 +2481,10 @@
         <v>860</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
     </row>
   </sheetData>
@@ -2525,7 +2525,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 22/10/2026 17:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 22/10/2026 23:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 22/10/2026 23:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 23/10/2026 00:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -733,7 +733,7 @@
         <v>44</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H8" s="11" t="n">
         <v>1.5</v>
@@ -767,10 +767,10 @@
         <v>47</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -801,7 +801,7 @@
         <v>44</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H10" s="11" t="n">
         <v>0.2</v>
@@ -835,10 +835,10 @@
         <v>39</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>9.199999999999999</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -903,10 +903,10 @@
         <v>35</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -1005,10 +1005,10 @@
         <v>44</v>
       </c>
       <c r="G16" s="10" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H16" s="11" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -1073,10 +1073,10 @@
         <v>37</v>
       </c>
       <c r="G18" s="10" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H18" s="11" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -1141,7 +1141,7 @@
         <v>44</v>
       </c>
       <c r="G20" s="10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H20" s="11" t="n">
         <v>0</v>
@@ -1243,10 +1243,10 @@
         <v>45</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H23" s="7" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -1773,10 +1773,10 @@
         <v>1464</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>482</v>
+        <v>448</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
     </row>
   </sheetData>
@@ -1817,7 +1817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 22/10/2026 23:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 23/10/2026 00:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -1969,7 +1969,7 @@
         <v>44</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G8" s="11" t="n">
         <v>1.5</v>
@@ -1998,10 +1998,10 @@
         <v>47</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -2027,7 +2027,7 @@
         <v>44</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G10" s="11" t="n">
         <v>0.2</v>
@@ -2056,10 +2056,10 @@
         <v>39</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>9.199999999999999</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -2114,10 +2114,10 @@
         <v>35</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -2201,10 +2201,10 @@
         <v>44</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -2259,10 +2259,10 @@
         <v>37</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -2317,7 +2317,7 @@
         <v>44</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G20" s="11" t="n">
         <v>0</v>
@@ -2404,10 +2404,10 @@
         <v>45</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -2481,10 +2481,10 @@
         <v>860</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>326</v>
+        <v>292</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
     </row>
   </sheetData>
@@ -2525,7 +2525,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 22/10/2026 23:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 23/10/2026 00:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 23/10/2026 00:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 23/10/2026 11:11 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
         <v>10</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -1039,7 +1039,7 @@
         <v>33</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H17" s="7" t="n">
         <v>2.3</v>
@@ -1773,7 +1773,7 @@
         <v>1464</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="H39" s="15" t="n">
         <v>1.7</v>
@@ -1817,7 +1817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 23/10/2026 00:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 23/10/2026 11:11 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2117,7 @@
         <v>10</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -2230,7 +2230,7 @@
         <v>33</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G17" s="7" t="n">
         <v>2.3</v>
@@ -2481,7 +2481,7 @@
         <v>860</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="G26" s="15" t="n">
         <v>2.1</v>
@@ -2525,7 +2525,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 23/10/2026 00:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 23/10/2026 11:11 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 23/10/2026 11:11 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 23/10/2026 11:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -1817,7 +1817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 23/10/2026 11:11 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 23/10/2026 11:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 23/10/2026 11:11 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 23/10/2026 11:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 23/10/2026 11:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 23/10/2026 12:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
         <v>10</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -1817,7 +1817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 23/10/2026 11:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 23/10/2026 12:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2117,7 @@
         <v>10</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -2525,7 +2525,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 23/10/2026 11:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 23/10/2026 12:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 23/10/2026 12:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 23/10/2026 14:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -903,10 +903,10 @@
         <v>35</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -1039,10 +1039,10 @@
         <v>33</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -1773,7 +1773,7 @@
         <v>1464</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="H39" s="15" t="n">
         <v>1.7</v>
@@ -1817,7 +1817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 23/10/2026 12:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 23/10/2026 14:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -2114,10 +2114,10 @@
         <v>35</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -2230,10 +2230,10 @@
         <v>33</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -2481,7 +2481,7 @@
         <v>860</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="G26" s="15" t="n">
         <v>2.1</v>
@@ -2525,7 +2525,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 23/10/2026 12:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 23/10/2026 14:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 23/10/2026 14:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 23/10/2026 17:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -699,10 +699,10 @@
         <v>46</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -903,10 +903,10 @@
         <v>35</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -1039,10 +1039,10 @@
         <v>33</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -1076,7 +1076,7 @@
         <v>14</v>
       </c>
       <c r="H18" s="11" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -1773,10 +1773,10 @@
         <v>1464</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
     </row>
   </sheetData>
@@ -1817,7 +1817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 23/10/2026 14:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 23/10/2026 17:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -1940,10 +1940,10 @@
         <v>46</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -2114,10 +2114,10 @@
         <v>35</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -2230,10 +2230,10 @@
         <v>33</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -2262,7 +2262,7 @@
         <v>14</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -2481,10 +2481,10 @@
         <v>860</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
     </row>
   </sheetData>
@@ -2525,7 +2525,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 23/10/2026 14:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 23/10/2026 17:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 23/10/2026 17:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 23/10/2026 18:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -900,13 +900,13 @@
         </is>
       </c>
       <c r="F13" s="6" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -1039,10 +1039,10 @@
         <v>33</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -1073,10 +1073,10 @@
         <v>37</v>
       </c>
       <c r="G18" s="10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H18" s="11" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -1770,10 +1770,10 @@
       <c r="D39" s="13" t="n"/>
       <c r="E39" s="13" t="n"/>
       <c r="F39" s="14" t="n">
-        <v>1464</v>
+        <v>1462</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="H39" s="15" t="n">
         <v>1.8</v>
@@ -1817,7 +1817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 23/10/2026 17:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 23/10/2026 18:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -2111,13 +2111,13 @@
         </is>
       </c>
       <c r="E13" s="6" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -2230,10 +2230,10 @@
         <v>33</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -2259,10 +2259,10 @@
         <v>37</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -2478,10 +2478,10 @@
       <c r="C26" s="13" t="n"/>
       <c r="D26" s="13" t="n"/>
       <c r="E26" s="14" t="n">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="G26" s="15" t="n">
         <v>2.2</v>
@@ -2525,7 +2525,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 23/10/2026 17:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 23/10/2026 18:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 23/10/2026 18:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 24/10/2026 00:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
         <v>7</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -665,7 +665,7 @@
         <v>47</v>
       </c>
       <c r="G6" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H6" s="11" t="n">
         <v>0</v>
@@ -770,7 +770,7 @@
         <v>3</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -801,10 +801,10 @@
         <v>44</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H10" s="11" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -835,10 +835,10 @@
         <v>39</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -869,10 +869,10 @@
         <v>45</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H12" s="11" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -900,13 +900,13 @@
         </is>
       </c>
       <c r="F13" s="6" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -1039,10 +1039,10 @@
         <v>33</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>3.8</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -1073,10 +1073,10 @@
         <v>37</v>
       </c>
       <c r="G18" s="10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H18" s="11" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -1107,10 +1107,10 @@
         <v>35</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -1770,10 +1770,10 @@
       <c r="D39" s="13" t="n"/>
       <c r="E39" s="13" t="n"/>
       <c r="F39" s="14" t="n">
-        <v>1462</v>
+        <v>1457</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="H39" s="15" t="n">
         <v>1.8</v>
@@ -1817,7 +1817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 23/10/2026 18:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 24/10/2026 00:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -1885,7 +1885,7 @@
         <v>7</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -1911,7 +1911,7 @@
         <v>47</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6" s="11" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>3</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -2027,10 +2027,10 @@
         <v>44</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -2056,10 +2056,10 @@
         <v>39</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -2085,10 +2085,10 @@
         <v>45</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -2111,13 +2111,13 @@
         </is>
       </c>
       <c r="E13" s="6" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -2230,10 +2230,10 @@
         <v>33</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>3.8</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -2259,10 +2259,10 @@
         <v>37</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -2288,10 +2288,10 @@
         <v>35</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -2478,13 +2478,13 @@
       <c r="C26" s="13" t="n"/>
       <c r="D26" s="13" t="n"/>
       <c r="E26" s="14" t="n">
-        <v>858</v>
+        <v>853</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>306</v>
+        <v>295</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
     </row>
   </sheetData>
@@ -2525,7 +2525,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 23/10/2026 18:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 24/10/2026 00:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 24/10/2026 00:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 24/10/2026 07:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
         <v>16</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -1817,7 +1817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 24/10/2026 00:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 24/10/2026 07:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2117,7 @@
         <v>16</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -2525,7 +2525,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 24/10/2026 00:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 24/10/2026 07:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 24/10/2026 07:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 24/10/2026 08:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -631,7 +631,7 @@
         <v>44</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H5" s="7" t="n">
         <v>0.5</v>
@@ -767,7 +767,7 @@
         <v>47</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H9" s="7" t="n">
         <v>0.1</v>
@@ -1773,7 +1773,7 @@
         <v>1457</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="H39" s="15" t="n">
         <v>1.8</v>
@@ -1817,7 +1817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 24/10/2026 07:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 24/10/2026 08:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
         <v>44</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G5" s="7" t="n">
         <v>0.5</v>
@@ -1998,7 +1998,7 @@
         <v>47</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G9" s="7" t="n">
         <v>0.1</v>
@@ -2481,7 +2481,7 @@
         <v>853</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="G26" s="15" t="n">
         <v>2.3</v>
@@ -2525,7 +2525,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 24/10/2026 07:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 24/10/2026 08:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 24/10/2026 08:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 24/10/2026 09:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
         <v>46</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H7" s="7" t="n">
         <v>1.2</v>
@@ -764,7 +764,7 @@
         </is>
       </c>
       <c r="F9" s="6" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>4</v>
@@ -1770,10 +1770,10 @@
       <c r="D39" s="13" t="n"/>
       <c r="E39" s="13" t="n"/>
       <c r="F39" s="14" t="n">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H39" s="15" t="n">
         <v>1.8</v>
@@ -1817,7 +1817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 24/10/2026 08:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 24/10/2026 09:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -1940,7 +1940,7 @@
         <v>46</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>1.2</v>
@@ -1995,7 +1995,7 @@
         </is>
       </c>
       <c r="E9" s="6" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>4</v>
@@ -2478,10 +2478,10 @@
       <c r="C26" s="13" t="n"/>
       <c r="D26" s="13" t="n"/>
       <c r="E26" s="14" t="n">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="G26" s="15" t="n">
         <v>2.3</v>
@@ -2525,7 +2525,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 24/10/2026 08:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 24/10/2026 09:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 24/10/2026 09:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 24/10/2026 10:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
         <v>46</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H7" s="7" t="n">
         <v>1.2</v>
@@ -801,7 +801,7 @@
         <v>44</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H10" s="11" t="n">
         <v>0.3</v>
@@ -903,7 +903,7 @@
         <v>28</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H13" s="7" t="n">
         <v>3.7</v>
@@ -1042,7 +1042,7 @@
         <v>25</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -1773,7 +1773,7 @@
         <v>1458</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="H39" s="15" t="n">
         <v>1.8</v>
@@ -1817,7 +1817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 24/10/2026 09:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 24/10/2026 10:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -1940,7 +1940,7 @@
         <v>46</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>1.2</v>
@@ -2027,7 +2027,7 @@
         <v>44</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G10" s="11" t="n">
         <v>0.3</v>
@@ -2114,7 +2114,7 @@
         <v>28</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G13" s="7" t="n">
         <v>3.7</v>
@@ -2233,7 +2233,7 @@
         <v>25</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -2481,7 +2481,7 @@
         <v>854</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="G26" s="15" t="n">
         <v>2.3</v>
@@ -2525,7 +2525,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 24/10/2026 09:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 24/10/2026 10:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 24/10/2026 10:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 24/10/2026 11:00 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -733,7 +733,7 @@
         <v>44</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H8" s="11" t="n">
         <v>1.5</v>
@@ -767,10 +767,10 @@
         <v>48</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -801,10 +801,10 @@
         <v>44</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H10" s="11" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -906,7 +906,7 @@
         <v>17</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -937,10 +937,10 @@
         <v>40</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H14" s="11" t="n">
-        <v>11.4</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -1042,7 +1042,7 @@
         <v>25</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -1773,10 +1773,10 @@
         <v>1458</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
     </row>
   </sheetData>
@@ -1817,7 +1817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 24/10/2026 10:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 24/10/2026 11:00 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -1969,7 +1969,7 @@
         <v>44</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G8" s="11" t="n">
         <v>1.5</v>
@@ -1998,10 +1998,10 @@
         <v>48</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -2027,10 +2027,10 @@
         <v>44</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -2117,7 +2117,7 @@
         <v>17</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -2143,10 +2143,10 @@
         <v>40</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>11.4</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -2233,7 +2233,7 @@
         <v>25</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -2481,10 +2481,10 @@
         <v>854</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
     </row>
   </sheetData>
@@ -2525,7 +2525,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 24/10/2026 10:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 24/10/2026 11:00 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 24/10/2026 11:00 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 24/10/2026 11:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
         <v>5</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -906,7 +906,7 @@
         <v>17</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -937,7 +937,7 @@
         <v>40</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H14" s="11" t="n">
         <v>11.8</v>
@@ -1042,7 +1042,7 @@
         <v>25</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -1773,7 +1773,7 @@
         <v>1458</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H39" s="15" t="n">
         <v>1.9</v>
@@ -1817,7 +1817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 24/10/2026 11:00 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 24/10/2026 11:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -2001,7 +2001,7 @@
         <v>5</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -2117,7 +2117,7 @@
         <v>17</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -2143,7 +2143,7 @@
         <v>40</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G14" s="11" t="n">
         <v>11.8</v>
@@ -2233,7 +2233,7 @@
         <v>25</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -2481,7 +2481,7 @@
         <v>854</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="G26" s="15" t="n">
         <v>2.4</v>
@@ -2525,7 +2525,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 24/10/2026 11:00 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 24/10/2026 11:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 24/10/2026 11:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 24/10/2026 12:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
         <v>17</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -1817,7 +1817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 24/10/2026 11:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 24/10/2026 12:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2117,7 @@
         <v>17</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -2525,7 +2525,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 24/10/2026 11:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 24/10/2026 12:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 24/10/2026 12:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 24/10/2026 14:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -801,7 +801,7 @@
         <v>44</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H10" s="11" t="n">
         <v>0.6</v>
@@ -971,10 +971,10 @@
         <v>44</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -1042,7 +1042,7 @@
         <v>25</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -1773,7 +1773,7 @@
         <v>1458</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="H39" s="15" t="n">
         <v>1.9</v>
@@ -1817,7 +1817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 24/10/2026 12:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 24/10/2026 14:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -2027,7 +2027,7 @@
         <v>44</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G10" s="11" t="n">
         <v>0.6</v>
@@ -2172,10 +2172,10 @@
         <v>44</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -2233,7 +2233,7 @@
         <v>25</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -2481,7 +2481,7 @@
         <v>854</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="G26" s="15" t="n">
         <v>2.4</v>
@@ -2525,7 +2525,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 24/10/2026 12:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 24/10/2026 14:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 24/10/2026 14:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 24/10/2026 18:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -733,7 +733,7 @@
         <v>44</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H8" s="11" t="n">
         <v>1.5</v>
@@ -801,10 +801,10 @@
         <v>44</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H10" s="11" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -906,7 +906,7 @@
         <v>17</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -974,7 +974,7 @@
         <v>27</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -1008,7 +1008,7 @@
         <v>31</v>
       </c>
       <c r="H16" s="11" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -1076,7 +1076,7 @@
         <v>16</v>
       </c>
       <c r="H18" s="11" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -1773,7 +1773,7 @@
         <v>1458</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="H39" s="15" t="n">
         <v>1.9</v>
@@ -1817,7 +1817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 24/10/2026 14:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 24/10/2026 18:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -1969,7 +1969,7 @@
         <v>44</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G8" s="11" t="n">
         <v>1.5</v>
@@ -2027,10 +2027,10 @@
         <v>44</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -2117,7 +2117,7 @@
         <v>17</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -2175,7 +2175,7 @@
         <v>27</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -2204,7 +2204,7 @@
         <v>31</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -2262,7 +2262,7 @@
         <v>16</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -2481,7 +2481,7 @@
         <v>854</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="G26" s="15" t="n">
         <v>2.4</v>
@@ -2525,7 +2525,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 24/10/2026 14:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 24/10/2026 18:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 24/10/2026 18:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 24/10/2026 20:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
         <v>17</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -1076,7 +1076,7 @@
         <v>16</v>
       </c>
       <c r="H18" s="11" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -1817,7 +1817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 24/10/2026 18:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 24/10/2026 20:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2117,7 @@
         <v>17</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -2262,7 +2262,7 @@
         <v>16</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -2484,7 +2484,7 @@
         <v>310</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
     </row>
   </sheetData>
@@ -2525,7 +2525,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 24/10/2026 18:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 24/10/2026 20:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 24/10/2026 20:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 24/10/2026 21:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -1817,7 +1817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 24/10/2026 20:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 24/10/2026 21:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 24/10/2026 20:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 24/10/2026 21:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 24/10/2026 21:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 25/10/2026 07:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -631,10 +631,10 @@
         <v>44</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -733,10 +733,10 @@
         <v>44</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H8" s="11" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -835,10 +835,10 @@
         <v>39</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -869,10 +869,10 @@
         <v>45</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H12" s="11" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -900,13 +900,13 @@
         </is>
       </c>
       <c r="F13" s="6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G13" s="6" t="n">
         <v>17</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -937,10 +937,10 @@
         <v>40</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H14" s="11" t="n">
-        <v>11.8</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -971,10 +971,10 @@
         <v>44</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -1005,10 +1005,10 @@
         <v>44</v>
       </c>
       <c r="G16" s="10" t="n">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="H16" s="11" t="n">
-        <v>4.5</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -1042,7 +1042,7 @@
         <v>25</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -1076,7 +1076,7 @@
         <v>16</v>
       </c>
       <c r="H18" s="11" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -1107,10 +1107,10 @@
         <v>35</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>1.8</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -1175,10 +1175,10 @@
         <v>40</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
@@ -1243,10 +1243,10 @@
         <v>45</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="H23" s="7" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -1311,10 +1311,10 @@
         <v>28</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H25" s="7" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1">
@@ -1770,13 +1770,13 @@
       <c r="D39" s="13" t="n"/>
       <c r="E39" s="13" t="n"/>
       <c r="F39" s="14" t="n">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>466</v>
+        <v>408</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
     </row>
   </sheetData>
@@ -1817,7 +1817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 24/10/2026 21:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 25/10/2026 07:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -1882,10 +1882,10 @@
         <v>44</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -1969,10 +1969,10 @@
         <v>44</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -2056,10 +2056,10 @@
         <v>39</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -2085,10 +2085,10 @@
         <v>45</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -2111,13 +2111,13 @@
         </is>
       </c>
       <c r="E13" s="6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>17</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -2143,10 +2143,10 @@
         <v>40</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>11.8</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -2172,10 +2172,10 @@
         <v>44</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -2201,10 +2201,10 @@
         <v>44</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>4.5</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -2233,7 +2233,7 @@
         <v>25</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -2262,7 +2262,7 @@
         <v>16</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -2288,10 +2288,10 @@
         <v>35</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>1.8</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -2346,10 +2346,10 @@
         <v>40</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
@@ -2404,10 +2404,10 @@
         <v>45</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -2462,10 +2462,10 @@
         <v>28</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="26" ht="26" customHeight="1">
@@ -2478,13 +2478,13 @@
       <c r="C26" s="13" t="n"/>
       <c r="D26" s="13" t="n"/>
       <c r="E26" s="14" t="n">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>310</v>
+        <v>252</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -2525,7 +2525,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 24/10/2026 21:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 25/10/2026 07:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 25/10/2026 07:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 26/10/2026 08:00 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -631,10 +631,10 @@
         <v>44</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -699,10 +699,10 @@
         <v>46</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -733,10 +733,10 @@
         <v>44</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="H8" s="11" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -767,10 +767,10 @@
         <v>48</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -801,10 +801,10 @@
         <v>44</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H10" s="11" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -835,10 +835,10 @@
         <v>39</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -869,10 +869,10 @@
         <v>45</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H12" s="11" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -906,7 +906,7 @@
         <v>17</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -937,10 +937,10 @@
         <v>40</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H14" s="11" t="n">
-        <v>10.7</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -971,10 +971,10 @@
         <v>44</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -1005,10 +1005,10 @@
         <v>44</v>
       </c>
       <c r="G16" s="10" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H16" s="11" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -1039,10 +1039,10 @@
         <v>33</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>5.8</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -1073,10 +1073,10 @@
         <v>37</v>
       </c>
       <c r="G18" s="10" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="H18" s="11" t="n">
-        <v>4.6</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -1107,10 +1107,10 @@
         <v>35</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -1175,10 +1175,10 @@
         <v>40</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>3.2</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
@@ -1243,10 +1243,10 @@
         <v>45</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="H23" s="7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -1311,10 +1311,10 @@
         <v>28</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H25" s="7" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1">
@@ -1773,10 +1773,10 @@
         <v>1457</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>408</v>
+        <v>337</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>
@@ -1817,7 +1817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 25/10/2026 07:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 26/10/2026 08:00 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -1882,10 +1882,10 @@
         <v>44</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -1940,10 +1940,10 @@
         <v>46</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -1969,10 +1969,10 @@
         <v>44</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -1998,10 +1998,10 @@
         <v>48</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -2027,10 +2027,10 @@
         <v>44</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -2056,10 +2056,10 @@
         <v>39</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -2085,10 +2085,10 @@
         <v>45</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -2117,7 +2117,7 @@
         <v>17</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -2143,10 +2143,10 @@
         <v>40</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>10.7</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -2172,10 +2172,10 @@
         <v>44</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -2201,10 +2201,10 @@
         <v>44</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -2230,10 +2230,10 @@
         <v>33</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>5.8</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -2259,10 +2259,10 @@
         <v>37</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>4.6</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -2288,10 +2288,10 @@
         <v>35</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -2346,10 +2346,10 @@
         <v>40</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>3.2</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
@@ -2404,10 +2404,10 @@
         <v>45</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -2462,10 +2462,10 @@
         <v>28</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" ht="26" customHeight="1">
@@ -2481,10 +2481,10 @@
         <v>853</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>252</v>
+        <v>181</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>
@@ -2525,7 +2525,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 25/10/2026 07:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 26/10/2026 08:00 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 26/10/2026 08:00 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 26/10/2026 11:29 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -631,10 +631,10 @@
         <v>44</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -770,7 +770,7 @@
         <v>6</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -801,7 +801,7 @@
         <v>44</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H10" s="11" t="n">
         <v>1</v>
@@ -1005,7 +1005,7 @@
         <v>44</v>
       </c>
       <c r="G16" s="10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H16" s="11" t="n">
         <v>3.2</v>
@@ -1039,10 +1039,10 @@
         <v>33</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -1773,7 +1773,7 @@
         <v>1457</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="H39" s="15" t="n">
         <v>1.3</v>
@@ -1817,7 +1817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 26/10/2026 08:00 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 26/10/2026 11:29 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -1882,10 +1882,10 @@
         <v>44</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -2001,7 +2001,7 @@
         <v>6</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -2027,7 +2027,7 @@
         <v>44</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G10" s="11" t="n">
         <v>1</v>
@@ -2201,7 +2201,7 @@
         <v>44</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G16" s="11" t="n">
         <v>3.2</v>
@@ -2230,10 +2230,10 @@
         <v>33</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -2481,7 +2481,7 @@
         <v>853</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="G26" s="15" t="n">
         <v>1.4</v>
@@ -2525,7 +2525,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 26/10/2026 08:00 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 26/10/2026 11:29 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 26/10/2026 11:29 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 27/10/2026 13:50 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -631,10 +631,10 @@
         <v>44</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -699,7 +699,7 @@
         <v>46</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H7" s="7" t="n">
         <v>0.3</v>
@@ -733,7 +733,7 @@
         <v>44</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H8" s="11" t="n">
         <v>0.4</v>
@@ -767,10 +767,10 @@
         <v>48</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -801,10 +801,10 @@
         <v>44</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H10" s="11" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -869,7 +869,7 @@
         <v>45</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H12" s="11" t="n">
         <v>0.5</v>
@@ -903,10 +903,10 @@
         <v>27</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -937,10 +937,10 @@
         <v>40</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H14" s="11" t="n">
-        <v>7.6</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -971,10 +971,10 @@
         <v>44</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -1005,10 +1005,10 @@
         <v>44</v>
       </c>
       <c r="G16" s="10" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="H16" s="11" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -1039,10 +1039,10 @@
         <v>33</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -1073,10 +1073,10 @@
         <v>37</v>
       </c>
       <c r="G18" s="10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H18" s="11" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -1175,10 +1175,10 @@
         <v>40</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
@@ -1311,7 +1311,7 @@
         <v>28</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H25" s="7" t="n">
         <v>0</v>
@@ -1773,10 +1773,10 @@
         <v>1457</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>
@@ -1817,7 +1817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 26/10/2026 11:29 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 27/10/2026 13:50 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -1882,10 +1882,10 @@
         <v>44</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -1940,7 +1940,7 @@
         <v>46</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>0.3</v>
@@ -1969,7 +1969,7 @@
         <v>44</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G8" s="11" t="n">
         <v>0.4</v>
@@ -1998,10 +1998,10 @@
         <v>48</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -2027,10 +2027,10 @@
         <v>44</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -2085,7 +2085,7 @@
         <v>45</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G12" s="11" t="n">
         <v>0.5</v>
@@ -2114,10 +2114,10 @@
         <v>27</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -2143,10 +2143,10 @@
         <v>40</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>7.6</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -2172,10 +2172,10 @@
         <v>44</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -2201,10 +2201,10 @@
         <v>44</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -2230,10 +2230,10 @@
         <v>33</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -2259,10 +2259,10 @@
         <v>37</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -2346,10 +2346,10 @@
         <v>40</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
@@ -2462,7 +2462,7 @@
         <v>28</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G25" s="7" t="n">
         <v>0</v>
@@ -2481,10 +2481,10 @@
         <v>853</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
     </row>
   </sheetData>
@@ -2525,7 +2525,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 26/10/2026 11:29 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 27/10/2026 13:50 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 27/10/2026 13:50 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 27/10/2026 14:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -801,10 +801,10 @@
         <v>44</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H10" s="11" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -937,10 +937,10 @@
         <v>40</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H14" s="11" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -1773,7 +1773,7 @@
         <v>1457</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="H39" s="15" t="n">
         <v>1.4</v>
@@ -1817,7 +1817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 27/10/2026 13:50 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 27/10/2026 14:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -2027,10 +2027,10 @@
         <v>44</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -2143,10 +2143,10 @@
         <v>40</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -2481,7 +2481,7 @@
         <v>853</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G26" s="15" t="n">
         <v>1.6</v>
@@ -2525,7 +2525,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 27/10/2026 13:50 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 27/10/2026 14:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 27/10/2026 14:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 27/10/2026 15:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -631,10 +631,10 @@
         <v>44</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -770,7 +770,7 @@
         <v>5</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -940,7 +940,7 @@
         <v>21</v>
       </c>
       <c r="H14" s="11" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -1773,7 +1773,7 @@
         <v>1457</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="H39" s="15" t="n">
         <v>1.4</v>
@@ -1817,7 +1817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 27/10/2026 14:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 27/10/2026 15:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -1882,10 +1882,10 @@
         <v>44</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -2001,7 +2001,7 @@
         <v>5</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -2146,7 +2146,7 @@
         <v>21</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -2481,7 +2481,7 @@
         <v>853</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="G26" s="15" t="n">
         <v>1.6</v>
@@ -2525,7 +2525,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 27/10/2026 14:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 27/10/2026 15:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 27/10/2026 15:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 27/10/2026 17:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -1817,7 +1817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 27/10/2026 15:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 27/10/2026 17:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 27/10/2026 15:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 27/10/2026 17:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 27/10/2026 17:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 27/10/2026 18:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -767,7 +767,7 @@
         <v>48</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H9" s="7" t="n">
         <v>0.6</v>
@@ -801,10 +801,10 @@
         <v>44</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H10" s="11" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -906,7 +906,7 @@
         <v>18</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -1005,10 +1005,10 @@
         <v>44</v>
       </c>
       <c r="G16" s="10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H16" s="11" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -1773,10 +1773,10 @@
         <v>1457</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>
@@ -1817,7 +1817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 27/10/2026 17:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 27/10/2026 18:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -1998,7 +1998,7 @@
         <v>48</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G9" s="7" t="n">
         <v>0.6</v>
@@ -2027,10 +2027,10 @@
         <v>44</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -2117,7 +2117,7 @@
         <v>18</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -2201,10 +2201,10 @@
         <v>44</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -2481,10 +2481,10 @@
         <v>853</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
     </row>
   </sheetData>
@@ -2525,7 +2525,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 27/10/2026 17:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 27/10/2026 18:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 27/10/2026 18:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 27/10/2026 19:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -767,10 +767,10 @@
         <v>48</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -804,7 +804,7 @@
         <v>14</v>
       </c>
       <c r="H10" s="11" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -906,7 +906,7 @@
         <v>18</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -1773,7 +1773,7 @@
         <v>1457</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="H39" s="15" t="n">
         <v>1.5</v>
@@ -1817,7 +1817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 27/10/2026 18:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 27/10/2026 19:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -1998,10 +1998,10 @@
         <v>48</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -2030,7 +2030,7 @@
         <v>14</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -2117,7 +2117,7 @@
         <v>18</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -2481,7 +2481,7 @@
         <v>853</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G26" s="15" t="n">
         <v>1.7</v>
@@ -2525,7 +2525,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 27/10/2026 18:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 27/10/2026 19:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 27/10/2026 19:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 27/10/2026 20:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
         <v>46</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H7" s="7" t="n">
         <v>0.3</v>
@@ -770,7 +770,7 @@
         <v>11</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -804,7 +804,7 @@
         <v>14</v>
       </c>
       <c r="H10" s="11" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -1773,7 +1773,7 @@
         <v>1457</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H39" s="15" t="n">
         <v>1.5</v>
@@ -1817,7 +1817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 27/10/2026 19:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 27/10/2026 20:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -1940,7 +1940,7 @@
         <v>46</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>0.3</v>
@@ -2001,7 +2001,7 @@
         <v>11</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -2030,7 +2030,7 @@
         <v>14</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -2481,7 +2481,7 @@
         <v>853</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G26" s="15" t="n">
         <v>1.7</v>
@@ -2525,7 +2525,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 27/10/2026 19:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 27/10/2026 20:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 27/10/2026 20:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 27/10/2026 21:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -835,7 +835,7 @@
         <v>39</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H11" s="7" t="n">
         <v>0.6</v>
@@ -937,10 +937,10 @@
         <v>40</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H14" s="11" t="n">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -1773,7 +1773,7 @@
         <v>1457</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="H39" s="15" t="n">
         <v>1.5</v>
@@ -1817,7 +1817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 27/10/2026 20:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 27/10/2026 21:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2056,7 @@
         <v>39</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G11" s="7" t="n">
         <v>0.6</v>
@@ -2143,10 +2143,10 @@
         <v>40</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -2481,7 +2481,7 @@
         <v>853</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="G26" s="15" t="n">
         <v>1.7</v>
@@ -2525,7 +2525,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 27/10/2026 20:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 27/10/2026 21:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 27/10/2026 21:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 28/10/2026 11:00 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -631,10 +631,10 @@
         <v>44</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -665,7 +665,7 @@
         <v>47</v>
       </c>
       <c r="G6" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" s="11" t="n">
         <v>0</v>
@@ -702,7 +702,7 @@
         <v>9</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -767,10 +767,10 @@
         <v>48</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -801,10 +801,10 @@
         <v>44</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H10" s="11" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -869,10 +869,10 @@
         <v>45</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H12" s="11" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -900,13 +900,13 @@
         </is>
       </c>
       <c r="F13" s="6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -937,10 +937,10 @@
         <v>40</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H14" s="11" t="n">
-        <v>7.5</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -1005,10 +1005,10 @@
         <v>44</v>
       </c>
       <c r="G16" s="10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H16" s="11" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -1073,10 +1073,10 @@
         <v>37</v>
       </c>
       <c r="G18" s="10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H18" s="11" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -1175,10 +1175,10 @@
         <v>40</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
@@ -1770,13 +1770,13 @@
       <c r="D39" s="13" t="n"/>
       <c r="E39" s="13" t="n"/>
       <c r="F39" s="14" t="n">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>
@@ -1817,7 +1817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 27/10/2026 21:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 28/10/2026 11:00 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -1882,10 +1882,10 @@
         <v>44</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -1911,7 +1911,7 @@
         <v>47</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" s="11" t="n">
         <v>0</v>
@@ -1943,7 +1943,7 @@
         <v>9</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -1998,10 +1998,10 @@
         <v>48</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -2027,10 +2027,10 @@
         <v>44</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -2085,10 +2085,10 @@
         <v>45</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -2111,13 +2111,13 @@
         </is>
       </c>
       <c r="E13" s="6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -2143,10 +2143,10 @@
         <v>40</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>7.5</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -2201,10 +2201,10 @@
         <v>44</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -2259,10 +2259,10 @@
         <v>37</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -2346,10 +2346,10 @@
         <v>40</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
@@ -2478,13 +2478,13 @@
       <c r="C26" s="13" t="n"/>
       <c r="D26" s="13" t="n"/>
       <c r="E26" s="14" t="n">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
     </row>
   </sheetData>
@@ -2525,7 +2525,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 27/10/2026 21:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 28/10/2026 11:00 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 28/10/2026 11:00 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 28/10/2026 11:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -1817,7 +1817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 28/10/2026 11:00 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 28/10/2026 11:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 28/10/2026 11:00 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 28/10/2026 11:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 28/10/2026 11:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 28/10/2026 22:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -767,10 +767,10 @@
         <v>48</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -804,7 +804,7 @@
         <v>16</v>
       </c>
       <c r="H10" s="11" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -937,10 +937,10 @@
         <v>40</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H14" s="11" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -1005,10 +1005,10 @@
         <v>44</v>
       </c>
       <c r="G16" s="10" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="H16" s="11" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -1773,10 +1773,10 @@
         <v>1458</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>356</v>
+        <v>368</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>
@@ -1817,7 +1817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 28/10/2026 11:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 28/10/2026 22:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -1998,10 +1998,10 @@
         <v>48</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -2030,7 +2030,7 @@
         <v>16</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -2143,10 +2143,10 @@
         <v>40</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -2201,10 +2201,10 @@
         <v>44</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -2481,10 +2481,10 @@
         <v>854</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
     </row>
   </sheetData>
@@ -2525,7 +2525,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 28/10/2026 11:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 28/10/2026 22:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 28/10/2026 22:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 28/10/2026 23:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
         <v>20</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -1817,7 +1817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 28/10/2026 22:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 28/10/2026 23:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -2001,7 +2001,7 @@
         <v>20</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -2525,7 +2525,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 28/10/2026 22:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 28/10/2026 23:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 28/10/2026 23:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 29/10/2026 11:00 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -699,10 +699,10 @@
         <v>46</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -733,7 +733,7 @@
         <v>44</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H8" s="11" t="n">
         <v>0.4</v>
@@ -767,7 +767,7 @@
         <v>48</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H9" s="7" t="n">
         <v>3.1</v>
@@ -801,7 +801,7 @@
         <v>44</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H10" s="11" t="n">
         <v>3.3</v>
@@ -838,7 +838,7 @@
         <v>4</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -869,10 +869,10 @@
         <v>45</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H12" s="11" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -906,7 +906,7 @@
         <v>17</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -937,10 +937,10 @@
         <v>40</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H14" s="11" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -971,10 +971,10 @@
         <v>44</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -1073,10 +1073,10 @@
         <v>37</v>
       </c>
       <c r="G18" s="10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H18" s="11" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -1243,7 +1243,7 @@
         <v>45</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H23" s="7" t="n">
         <v>0</v>
@@ -1773,10 +1773,10 @@
         <v>1458</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>
@@ -1817,7 +1817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 28/10/2026 23:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 29/10/2026 11:00 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -1940,10 +1940,10 @@
         <v>46</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -1969,7 +1969,7 @@
         <v>44</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G8" s="11" t="n">
         <v>0.4</v>
@@ -1998,7 +1998,7 @@
         <v>48</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G9" s="7" t="n">
         <v>3.1</v>
@@ -2027,7 +2027,7 @@
         <v>44</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G10" s="11" t="n">
         <v>3.3</v>
@@ -2059,7 +2059,7 @@
         <v>4</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -2085,10 +2085,10 @@
         <v>45</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -2117,7 +2117,7 @@
         <v>17</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -2143,10 +2143,10 @@
         <v>40</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -2172,10 +2172,10 @@
         <v>44</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -2259,10 +2259,10 @@
         <v>37</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -2404,7 +2404,7 @@
         <v>45</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" s="7" t="n">
         <v>0</v>
@@ -2481,10 +2481,10 @@
         <v>854</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
     </row>
   </sheetData>
@@ -2525,7 +2525,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 28/10/2026 23:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 29/10/2026 11:00 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 29/10/2026 11:00 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 29/10/2026 11:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -1817,7 +1817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 29/10/2026 11:00 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 29/10/2026 11:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 29/10/2026 11:00 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 29/10/2026 11:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 29/10/2026 11:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 29/10/2026 14:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -767,10 +767,10 @@
         <v>48</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -1773,10 +1773,10 @@
         <v>1458</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>
@@ -1817,7 +1817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 29/10/2026 11:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 29/10/2026 14:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -1998,10 +1998,10 @@
         <v>48</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -2481,10 +2481,10 @@
         <v>854</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
     </row>
   </sheetData>
@@ -2525,7 +2525,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 29/10/2026 11:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 29/10/2026 14:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 29/10/2026 14:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 30/10/2026 07:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
         <v>28</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -665,10 +665,10 @@
         <v>47</v>
       </c>
       <c r="G6" s="10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H6" s="11" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -733,7 +733,7 @@
         <v>44</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H8" s="11" t="n">
         <v>0.4</v>
@@ -764,13 +764,13 @@
         </is>
       </c>
       <c r="F9" s="6" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>3.4</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -801,10 +801,10 @@
         <v>44</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H10" s="11" t="n">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -835,10 +835,10 @@
         <v>39</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -903,10 +903,10 @@
         <v>28</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -937,10 +937,10 @@
         <v>40</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H14" s="11" t="n">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -974,7 +974,7 @@
         <v>13</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -1005,10 +1005,10 @@
         <v>44</v>
       </c>
       <c r="G16" s="10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H16" s="11" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -1039,10 +1039,10 @@
         <v>33</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -1076,7 +1076,7 @@
         <v>7</v>
       </c>
       <c r="H18" s="11" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -1141,7 +1141,7 @@
         <v>44</v>
       </c>
       <c r="G20" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H20" s="11" t="n">
         <v>0</v>
@@ -1175,10 +1175,10 @@
         <v>40</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
@@ -1770,13 +1770,13 @@
       <c r="D39" s="13" t="n"/>
       <c r="E39" s="13" t="n"/>
       <c r="F39" s="14" t="n">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
     </row>
   </sheetData>
@@ -1817,7 +1817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 29/10/2026 14:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 30/10/2026 07:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -1885,7 +1885,7 @@
         <v>28</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -1911,10 +1911,10 @@
         <v>47</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -1969,7 +1969,7 @@
         <v>44</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G8" s="11" t="n">
         <v>0.4</v>
@@ -1995,13 +1995,13 @@
         </is>
       </c>
       <c r="E9" s="6" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>3.4</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -2027,10 +2027,10 @@
         <v>44</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -2056,10 +2056,10 @@
         <v>39</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -2114,10 +2114,10 @@
         <v>28</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -2143,10 +2143,10 @@
         <v>40</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -2175,7 +2175,7 @@
         <v>13</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -2201,10 +2201,10 @@
         <v>44</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -2230,10 +2230,10 @@
         <v>33</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -2262,7 +2262,7 @@
         <v>7</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -2317,7 +2317,7 @@
         <v>44</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20" s="11" t="n">
         <v>0</v>
@@ -2346,10 +2346,10 @@
         <v>40</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
@@ -2478,13 +2478,13 @@
       <c r="C26" s="13" t="n"/>
       <c r="D26" s="13" t="n"/>
       <c r="E26" s="14" t="n">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
     </row>
   </sheetData>
@@ -2525,7 +2525,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 29/10/2026 14:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 30/10/2026 07:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 30/10/2026 07:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 30/10/2026 08:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -801,7 +801,7 @@
         <v>44</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H10" s="11" t="n">
         <v>4.4</v>
@@ -1036,13 +1036,13 @@
         </is>
       </c>
       <c r="F17" s="6" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G17" s="6" t="n">
         <v>19</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -1770,10 +1770,10 @@
       <c r="D39" s="13" t="n"/>
       <c r="E39" s="13" t="n"/>
       <c r="F39" s="14" t="n">
-        <v>1457</v>
+        <v>1454</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H39" s="15" t="n">
         <v>1.6</v>
@@ -1817,7 +1817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 30/10/2026 07:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 30/10/2026 08:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -2027,7 +2027,7 @@
         <v>44</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G10" s="11" t="n">
         <v>4.4</v>
@@ -2227,13 +2227,13 @@
         </is>
       </c>
       <c r="E17" s="6" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>19</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -2478,13 +2478,13 @@
       <c r="C26" s="13" t="n"/>
       <c r="D26" s="13" t="n"/>
       <c r="E26" s="14" t="n">
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
     </row>
   </sheetData>
@@ -2525,7 +2525,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 30/10/2026 07:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 30/10/2026 08:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 30/10/2026 08:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 30/10/2026 15:19 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -801,10 +801,10 @@
         <v>44</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H10" s="11" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -900,13 +900,13 @@
         </is>
       </c>
       <c r="F13" s="6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -1005,7 +1005,7 @@
         <v>44</v>
       </c>
       <c r="G16" s="10" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H16" s="11" t="n">
         <v>4.6</v>
@@ -1770,10 +1770,10 @@
       <c r="D39" s="13" t="n"/>
       <c r="E39" s="13" t="n"/>
       <c r="F39" s="14" t="n">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="H39" s="15" t="n">
         <v>1.6</v>
@@ -1817,7 +1817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 30/10/2026 08:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 30/10/2026 15:19 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -2027,10 +2027,10 @@
         <v>44</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -2111,13 +2111,13 @@
         </is>
       </c>
       <c r="E13" s="6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -2201,7 +2201,7 @@
         <v>44</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G16" s="11" t="n">
         <v>4.6</v>
@@ -2478,10 +2478,10 @@
       <c r="C26" s="13" t="n"/>
       <c r="D26" s="13" t="n"/>
       <c r="E26" s="14" t="n">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="G26" s="15" t="n">
         <v>1.9</v>
@@ -2525,7 +2525,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 30/10/2026 08:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 30/10/2026 15:19 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 30/10/2026 15:19 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 30/10/2026 15:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -1817,7 +1817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 30/10/2026 15:19 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 30/10/2026 15:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 30/10/2026 15:19 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 30/10/2026 15:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 30/10/2026 15:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 30/10/2026 17:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -801,7 +801,7 @@
         <v>44</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H10" s="11" t="n">
         <v>4.7</v>
@@ -1175,7 +1175,7 @@
         <v>40</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H21" s="7" t="n">
         <v>0.1</v>
@@ -1773,7 +1773,7 @@
         <v>1453</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="H39" s="15" t="n">
         <v>1.6</v>
@@ -1817,7 +1817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 30/10/2026 15:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 30/10/2026 17:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -2027,7 +2027,7 @@
         <v>44</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G10" s="11" t="n">
         <v>4.7</v>
@@ -2346,7 +2346,7 @@
         <v>40</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G21" s="7" t="n">
         <v>0.1</v>
@@ -2481,7 +2481,7 @@
         <v>849</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="G26" s="15" t="n">
         <v>1.9</v>
@@ -2525,7 +2525,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 30/10/2026 15:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 30/10/2026 17:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 30/10/2026 17:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 30/10/2026 20:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -631,7 +631,7 @@
         <v>44</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H5" s="7" t="n">
         <v>2.4</v>
@@ -699,7 +699,7 @@
         <v>46</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H7" s="7" t="n">
         <v>0.1</v>
@@ -801,10 +801,10 @@
         <v>44</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H10" s="11" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -903,10 +903,10 @@
         <v>27</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -1008,7 +1008,7 @@
         <v>33</v>
       </c>
       <c r="H16" s="11" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -1073,10 +1073,10 @@
         <v>37</v>
       </c>
       <c r="G18" s="10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H18" s="11" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -1773,10 +1773,10 @@
         <v>1453</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
     </row>
   </sheetData>
@@ -1817,7 +1817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 30/10/2026 17:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 30/10/2026 20:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
         <v>44</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G5" s="7" t="n">
         <v>2.4</v>
@@ -1940,7 +1940,7 @@
         <v>46</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>0.1</v>
@@ -2027,10 +2027,10 @@
         <v>44</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -2114,10 +2114,10 @@
         <v>27</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -2204,7 +2204,7 @@
         <v>33</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -2259,10 +2259,10 @@
         <v>37</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -2481,10 +2481,10 @@
         <v>849</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
     </row>
   </sheetData>
@@ -2525,7 +2525,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 30/10/2026 17:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 30/10/2026 20:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 30/10/2026 20:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 30/10/2026 21:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -801,10 +801,10 @@
         <v>44</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H10" s="11" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -903,7 +903,7 @@
         <v>27</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H13" s="7" t="n">
         <v>6</v>
@@ -1008,7 +1008,7 @@
         <v>33</v>
       </c>
       <c r="H16" s="11" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -1773,7 +1773,7 @@
         <v>1453</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="H39" s="15" t="n">
         <v>1.7</v>
@@ -1817,7 +1817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 30/10/2026 20:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 30/10/2026 21:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -2027,10 +2027,10 @@
         <v>44</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -2114,7 +2114,7 @@
         <v>27</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G13" s="7" t="n">
         <v>6</v>
@@ -2204,7 +2204,7 @@
         <v>33</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -2481,7 +2481,7 @@
         <v>849</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="G26" s="15" t="n">
         <v>2.1</v>
@@ -2525,7 +2525,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 30/10/2026 20:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 30/10/2026 21:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 30/10/2026 21:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 31/10/2026 07:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         <v>8</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -770,7 +770,7 @@
         <v>39</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -801,10 +801,10 @@
         <v>44</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H10" s="11" t="n">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -835,10 +835,10 @@
         <v>39</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -903,10 +903,10 @@
         <v>27</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>6</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -1039,10 +1039,10 @@
         <v>30</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>5.3</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -1073,10 +1073,10 @@
         <v>37</v>
       </c>
       <c r="G18" s="10" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H18" s="11" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -1175,7 +1175,7 @@
         <v>40</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H21" s="7" t="n">
         <v>0.1</v>
@@ -1773,10 +1773,10 @@
         <v>1453</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>386</v>
+        <v>366</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
     </row>
   </sheetData>
@@ -1817,7 +1817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 30/10/2026 21:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 31/10/2026 07:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -1943,7 +1943,7 @@
         <v>8</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -2001,7 +2001,7 @@
         <v>39</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -2027,10 +2027,10 @@
         <v>44</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -2056,10 +2056,10 @@
         <v>39</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -2114,10 +2114,10 @@
         <v>27</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>6</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -2230,10 +2230,10 @@
         <v>30</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>5.3</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -2259,10 +2259,10 @@
         <v>37</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -2346,7 +2346,7 @@
         <v>40</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G21" s="7" t="n">
         <v>0.1</v>
@@ -2481,10 +2481,10 @@
         <v>849</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
     </row>
   </sheetData>
@@ -2525,7 +2525,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 30/10/2026 21:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 31/10/2026 07:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 31/10/2026 07:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 31/10/2026 08:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -1817,7 +1817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 31/10/2026 07:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 31/10/2026 08:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 31/10/2026 07:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 31/10/2026 08:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 31/10/2026 08:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 31/10/2026 09:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -665,10 +665,10 @@
         <v>47</v>
       </c>
       <c r="G6" s="10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H6" s="11" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -804,7 +804,7 @@
         <v>28</v>
       </c>
       <c r="H10" s="11" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -1773,7 +1773,7 @@
         <v>1453</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="H39" s="15" t="n">
         <v>1.6</v>
@@ -1817,7 +1817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 31/10/2026 08:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 31/10/2026 09:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -1911,10 +1911,10 @@
         <v>47</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -2030,7 +2030,7 @@
         <v>28</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -2481,10 +2481,10 @@
         <v>849</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
     </row>
   </sheetData>
@@ -2525,7 +2525,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 31/10/2026 08:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 31/10/2026 09:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 31/10/2026 09:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 31/10/2026 10:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -665,10 +665,10 @@
         <v>47</v>
       </c>
       <c r="G6" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H6" s="11" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -801,7 +801,7 @@
         <v>44</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H10" s="11" t="n">
         <v>6.6</v>
@@ -1773,7 +1773,7 @@
         <v>1453</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="H39" s="15" t="n">
         <v>1.6</v>
@@ -1817,7 +1817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 31/10/2026 09:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 31/10/2026 10:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -1911,10 +1911,10 @@
         <v>47</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -2027,7 +2027,7 @@
         <v>44</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G10" s="11" t="n">
         <v>6.6</v>
@@ -2481,7 +2481,7 @@
         <v>849</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="G26" s="15" t="n">
         <v>1.9</v>
@@ -2525,7 +2525,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 31/10/2026 09:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 31/10/2026 10:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 31/10/2026 10:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 31/10/2026 16:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
         <v>29</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -665,10 +665,10 @@
         <v>47</v>
       </c>
       <c r="G6" s="10" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H6" s="11" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -702,7 +702,7 @@
         <v>8</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -1005,10 +1005,10 @@
         <v>44</v>
       </c>
       <c r="G16" s="10" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H16" s="11" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -1773,10 +1773,10 @@
         <v>1453</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
     </row>
   </sheetData>
@@ -1817,7 +1817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 31/10/2026 10:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 31/10/2026 16:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -1885,7 +1885,7 @@
         <v>29</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -1911,10 +1911,10 @@
         <v>47</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -1943,7 +1943,7 @@
         <v>8</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -2201,10 +2201,10 @@
         <v>44</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -2481,10 +2481,10 @@
         <v>849</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -2525,7 +2525,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 31/10/2026 10:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 31/10/2026 16:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 31/10/2026 16:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 31/10/2026 17:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
         <v>29</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -668,7 +668,7 @@
         <v>12</v>
       </c>
       <c r="H6" s="11" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -1817,7 +1817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 31/10/2026 16:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 31/10/2026 17:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -1885,7 +1885,7 @@
         <v>29</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -1914,7 +1914,7 @@
         <v>12</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -2525,7 +2525,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 31/10/2026 16:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 31/10/2026 17:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 31/10/2026 17:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 31/10/2026 18:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -1817,7 +1817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 31/10/2026 17:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 31/10/2026 18:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 31/10/2026 17:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 31/10/2026 18:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>

--- a/BaoCao_KAV.xlsx
+++ b/BaoCao_KAV.xlsx
@@ -556,7 +556,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 31/10/2026 18:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 31/10/2026 20:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -631,10 +631,10 @@
         <v>44</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -665,10 +665,10 @@
         <v>47</v>
       </c>
       <c r="G6" s="10" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="H6" s="11" t="n">
-        <v>2.7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -767,10 +767,10 @@
         <v>47</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -801,10 +801,10 @@
         <v>44</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H10" s="11" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -906,7 +906,7 @@
         <v>14</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -1005,10 +1005,10 @@
         <v>44</v>
       </c>
       <c r="G16" s="10" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H16" s="11" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -1773,10 +1773,10 @@
         <v>1453</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>380</v>
+        <v>400</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
     </row>
   </sheetData>
@@ -1817,7 +1817,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 31/10/2026 18:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 31/10/2026 20:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
@@ -1882,10 +1882,10 @@
         <v>44</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -1911,10 +1911,10 @@
         <v>47</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>2.7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -1998,10 +1998,10 @@
         <v>47</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -2027,10 +2027,10 @@
         <v>44</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -2117,7 +2117,7 @@
         <v>14</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -2201,10 +2201,10 @@
         <v>44</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -2481,10 +2481,10 @@
         <v>849</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>224</v>
+        <v>244</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
     </row>
   </sheetData>
@@ -2525,7 +2525,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Thời gian thống kê: 31/10/2026 18:20 | Trường: THCS&amp;THPT MONG THỌ</t>
+          <t>Thời gian thống kê: 31/10/2026 20:20 | Trường: THCS&amp;THPT MONG THỌ</t>
         </is>
       </c>
     </row>
